--- a/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-24 - 2026-08-30).xlsx
+++ b/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-24 - 2026-08-30).xlsx
@@ -425,7 +425,7 @@
     <t>Jardim Tavares-Campina Grande</t>
   </si>
   <si>
-    <t>Alcantara de Medeiros Junior,Pedro</t>
+    <t>OLIVEIRA,MARCOS VICTOR SILVA</t>
   </si>
   <si>
     <t>Fazenda Santa Genebra-Campinas</t>
@@ -506,9 +506,6 @@
     <t>Joao Pessoa</t>
   </si>
   <si>
-    <t>OLIVEIRA,MARCOS VICTOR SILVA</t>
-  </si>
-  <si>
     <t>Joinville</t>
   </si>
   <si>
@@ -806,9 +803,6 @@
     <t>Cachoeiro de Itapemirim</t>
   </si>
   <si>
-    <t>DURANTE,DANIEL BARROS and DANIELA PIMENTEL MOREIRA</t>
-  </si>
-  <si>
     <t>AP</t>
   </si>
   <si>
@@ -884,22 +878,22 @@
     <t>174</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>R$ 41.675,45</t>
-  </si>
-  <si>
-    <t>425.2</t>
-  </si>
-  <si>
-    <t>259.4</t>
-  </si>
-  <si>
-    <t>5.76</t>
-  </si>
-  <si>
-    <t>20.3</t>
+    <t>122</t>
+  </si>
+  <si>
+    <t>R$ 42.016,00</t>
+  </si>
+  <si>
+    <t>444.5</t>
+  </si>
+  <si>
+    <t>276.3</t>
+  </si>
+  <si>
+    <t>5.81</t>
+  </si>
+  <si>
+    <t>20.4</t>
   </si>
   <si>
     <t>7.8</t>
@@ -908,24 +902,27 @@
     <t>6.6</t>
   </si>
   <si>
-    <t>35.8%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
+    <t>34.8%</t>
+  </si>
+  <si>
+    <t>17.5%</t>
   </si>
   <si>
     <t>2.0%</t>
   </si>
   <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.2%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
     <t>6.1%</t>
   </si>
   <si>
@@ -935,40 +932,40 @@
     <t>4.2%</t>
   </si>
   <si>
-    <t>9052.0</t>
-  </si>
-  <si>
-    <t>7169.0</t>
-  </si>
-  <si>
-    <t>812.0</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>2120.0</t>
-  </si>
-  <si>
-    <t>602.0</t>
-  </si>
-  <si>
-    <t>77.0</t>
-  </si>
-  <si>
-    <t>2502.0</t>
-  </si>
-  <si>
-    <t>1051.0</t>
-  </si>
-  <si>
-    <t>1727.0</t>
+    <t>9558.0</t>
+  </si>
+  <si>
+    <t>7602.0</t>
+  </si>
+  <si>
+    <t>854.0</t>
+  </si>
+  <si>
+    <t>138.0</t>
+  </si>
+  <si>
+    <t>2226.0</t>
+  </si>
+  <si>
+    <t>630.0</t>
+  </si>
+  <si>
+    <t>78.0</t>
+  </si>
+  <si>
+    <t>2645.0</t>
+  </si>
+  <si>
+    <t>1111.0</t>
+  </si>
+  <si>
+    <t>1843.0</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>161.0</t>
+    <t>171.0</t>
   </si>
   <si>
     <t>1</t>
@@ -1748,7 +1745,7 @@
         <v>19513</v>
       </c>
       <c r="B3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C3" s="4">
         <v>51</v>
@@ -1779,61 +1776,61 @@
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="5">
-        <v>64133.334999999999</v>
+        <v>68470.880000000005</v>
       </c>
       <c r="N3" s="6">
-        <v>544</v>
+        <v>681</v>
       </c>
       <c r="O3" s="6">
-        <v>411</v>
+        <v>507</v>
       </c>
       <c r="P3" s="7">
-        <v>4.8985854243542439</v>
+        <v>5.3417033873343147</v>
       </c>
       <c r="Q3" s="8">
-        <v>15.323681995133819</v>
+        <v>15.947501577909271</v>
       </c>
       <c r="R3" s="8">
-        <v>4.5497933002481394</v>
+        <v>4.6258737903225802</v>
       </c>
       <c r="S3" s="8">
         <v>6</v>
       </c>
       <c r="T3" s="9">
-        <v>0.52554744525547448</v>
+        <v>0.48915187376725838</v>
       </c>
       <c r="U3" s="9">
-        <v>0.16545012165450121</v>
+        <v>0.18737672583826431</v>
       </c>
       <c r="V3" s="9">
-        <v>0.0048661800486618006</v>
+        <v>0.0039447731755424065</v>
       </c>
       <c r="W3" s="9">
-        <v>0.0024330900240000001</v>
+        <v>0.0019723865869999998</v>
       </c>
       <c r="X3" s="9">
-        <v>0.036496350364963501</v>
+        <v>0.033530571992110451</v>
       </c>
       <c r="Y3" s="9">
-        <v>0.019464720194647202</v>
+        <v>0.019723865877712032</v>
       </c>
       <c r="Z3" s="9">
         <v>0</v>
       </c>
       <c r="AA3" s="9">
-        <v>0.029197080291970802</v>
+        <v>0.031558185404339252</v>
       </c>
       <c r="AB3" s="9">
-        <v>0.026763990267639901</v>
+        <v>0.023668639053254437</v>
       </c>
       <c r="AC3" s="9">
-        <v>0.087591240875912413</v>
+        <v>0.11834319526627218</v>
       </c>
       <c r="AD3" s="6">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="AE3" s="6">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AF3" s="6">
         <v>2</v>
@@ -1842,25 +1839,25 @@
         <v>1</v>
       </c>
       <c r="AH3" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI3" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ3" s="6">
         <v>0</v>
       </c>
       <c r="AK3" s="6">
+        <v>16</v>
+      </c>
+      <c r="AL3" s="6">
         <v>12</v>
       </c>
-      <c r="AL3" s="6">
-        <v>11</v>
-      </c>
       <c r="AM3" s="6">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AN3" s="9">
-        <v>0.0048661800486618006</v>
+        <v>0.0039447731755424065</v>
       </c>
       <c r="AO3" s="6">
         <v>2</v>
@@ -2219,7 +2216,7 @@
         <v>19521</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2250,7 +2247,7 @@
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="5">
-        <v>88932.444999999992</v>
+        <v>76227.809999999983</v>
       </c>
       <c r="N6" s="6">
         <v>838</v>
@@ -3743,7 +3740,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>51</v>
@@ -3774,40 +3771,40 @@
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="5">
-        <v>42032.059999999998</v>
+        <v>42392.419999999998</v>
       </c>
       <c r="N16" s="6">
-        <v>390</v>
+        <v>458</v>
       </c>
       <c r="O16" s="6">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="P16" s="7">
-        <v>3.49280205655527</v>
+        <v>3.2640043763676152</v>
       </c>
       <c r="Q16" s="8">
-        <v>16.990420560747662</v>
+        <v>16.462756538461541</v>
       </c>
       <c r="R16" s="8">
-        <v>6.6011682242990659</v>
+        <v>6.3543588461538461</v>
       </c>
       <c r="S16" s="8">
         <v>7</v>
       </c>
       <c r="T16" s="9">
-        <v>0.46261682242990654</v>
+        <v>0.5</v>
       </c>
       <c r="U16" s="9">
-        <v>0.1542056074766355</v>
+        <v>0.17692307692307693</v>
       </c>
       <c r="V16" s="9">
-        <v>0.0093457943925233638</v>
+        <v>0.0076923076923076927</v>
       </c>
       <c r="W16" s="9">
         <v>0</v>
       </c>
       <c r="X16" s="9">
-        <v>0.10280373831775701</v>
+        <v>0.13461538461538461</v>
       </c>
       <c r="Y16" s="9">
         <v>0</v>
@@ -3816,19 +3813,19 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9">
-        <v>0.0046728971962616819</v>
+        <v>0.0038461538461538464</v>
       </c>
       <c r="AB16" s="9">
-        <v>0.0046728971962616819</v>
+        <v>0.0038461538461538464</v>
       </c>
       <c r="AC16" s="9">
-        <v>0.042056074766355138</v>
+        <v>0.04230769230769231</v>
       </c>
       <c r="AD16" s="6">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="AE16" s="6">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="AF16" s="6">
         <v>2</v>
@@ -3837,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="6">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="AI16" s="6">
         <v>0</v>
@@ -3852,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="AM16" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -4214,7 +4211,7 @@
         <v>19551</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>51</v>
@@ -4245,28 +4242,28 @@
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="5">
-        <v>55817.066666666658</v>
+        <v>60390.349999999999</v>
       </c>
       <c r="N19" s="6">
-        <v>465</v>
+        <v>587</v>
       </c>
       <c r="O19" s="6">
         <v>285</v>
       </c>
       <c r="P19" s="7">
-        <v>3.4596638655462182</v>
+        <v>3.5595238655462187</v>
       </c>
       <c r="Q19" s="8">
-        <v>15.82953192982456</v>
+        <v>16.0913162464986</v>
       </c>
       <c r="R19" s="8">
-        <v>4.4204442446043162</v>
+        <v>4.6172896551724136</v>
       </c>
       <c r="S19" s="8">
         <v>8</v>
       </c>
       <c r="T19" s="9">
-        <v>0.4631578947368421</v>
+        <v>0.43977591036414565</v>
       </c>
       <c r="U19" s="9">
         <v>0.19649122807017544</v>
@@ -4528,7 +4525,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>51</v>
@@ -4557,49 +4554,49 @@
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="5">
-        <v>52286.581666666665</v>
+        <v>55975.479999999996</v>
       </c>
       <c r="N21" s="6">
-        <v>409</v>
+        <v>512</v>
       </c>
       <c r="O21" s="6">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="P21" s="7">
-        <v>3.344417831325301</v>
+        <v>3.5740318095238095</v>
       </c>
       <c r="Q21" s="8">
-        <v>19.878365882352941</v>
+        <v>21.14723076923077</v>
       </c>
       <c r="R21" s="8">
-        <v>9.7780185039370089</v>
+        <v>10.820072445820434</v>
       </c>
       <c r="S21" s="8">
         <v>7</v>
       </c>
       <c r="T21" s="9">
-        <v>0.29411764705882354</v>
+        <v>0.24923076923076923</v>
       </c>
       <c r="U21" s="9">
-        <v>0.090196078431372548</v>
+        <v>0.095384615384615387</v>
       </c>
       <c r="V21" s="9">
-        <v>0.0039215686274509803</v>
+        <v>0.0061538461538461538</v>
       </c>
       <c r="W21" s="9">
-        <v>0.019607843137000001</v>
+        <v>0.015384615383999999</v>
       </c>
       <c r="X21" s="9">
-        <v>0.015686274509803921</v>
+        <v>0.018461538461538463</v>
       </c>
       <c r="Y21" s="9">
-        <v>0.0039215686274509803</v>
+        <v>0.0061538461538461538</v>
       </c>
       <c r="Z21" s="9">
         <v>0</v>
       </c>
       <c r="AA21" s="9">
-        <v>0.0078431372549019607</v>
+        <v>0.0092307692307692316</v>
       </c>
       <c r="AB21" s="9">
         <v>0</v>
@@ -4608,28 +4605,28 @@
         <v>0</v>
       </c>
       <c r="AD21" s="6">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AE21" s="6">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="AF21" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG21" s="6">
         <v>5</v>
       </c>
       <c r="AH21" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI21" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ21" s="6">
         <v>0</v>
       </c>
       <c r="AK21" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL21" s="6">
         <v>0</v>
@@ -4638,10 +4635,10 @@
         <v>0</v>
       </c>
       <c r="AN21" s="9">
-        <v>0.054901960784313725</v>
+        <v>0.058461538461538461</v>
       </c>
       <c r="AO21" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c t="s" r="AP21" s="4">
         <v>58</v>
@@ -4901,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="9">
-        <v>0</v>
+        <v>0.0043478260859999996</v>
       </c>
       <c r="X23" s="9">
         <v>0.047826086956521741</v>
@@ -4931,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="AG23" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" s="6">
         <v>11</v>
@@ -4997,7 +4994,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5028,82 +5025,82 @@
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="5">
-        <v>46096.738333333342</v>
+        <v>53148.700000000004</v>
       </c>
       <c r="N24" s="6">
-        <v>444</v>
+        <v>590</v>
       </c>
       <c r="O24" s="6">
-        <v>267</v>
+        <v>368</v>
       </c>
       <c r="P24" s="7">
-        <v>3.1253382882882885</v>
+        <v>3.0908887945670629</v>
       </c>
       <c r="Q24" s="8">
-        <v>19.387016479400749</v>
+        <v>18.824275543478262</v>
       </c>
       <c r="R24" s="8">
-        <v>8.6664081395348838</v>
+        <v>8.2006571830985919</v>
       </c>
       <c r="S24" s="8">
         <v>8</v>
       </c>
       <c r="T24" s="9">
-        <v>0.33707865168539325</v>
+        <v>0.33423913043478259</v>
       </c>
       <c r="U24" s="9">
-        <v>0.14232209737827714</v>
+        <v>0.14402173913043478</v>
       </c>
       <c r="V24" s="9">
-        <v>0.014981273408239701</v>
+        <v>0.010869565217391304</v>
       </c>
       <c r="W24" s="9">
-        <v>0.003745318352</v>
+        <v>0.0054347826080000002</v>
       </c>
       <c r="X24" s="9">
-        <v>0.07116104868913857</v>
+        <v>0.05434782608695652</v>
       </c>
       <c r="Y24" s="9">
-        <v>0.011235955056179775</v>
+        <v>0.010869565217391304</v>
       </c>
       <c r="Z24" s="9">
         <v>0</v>
       </c>
       <c r="AA24" s="9">
-        <v>0.059925093632958802</v>
+        <v>0.05434782608695652</v>
       </c>
       <c r="AB24" s="9">
-        <v>0.033707865168539325</v>
+        <v>0.051630434782608696</v>
       </c>
       <c r="AC24" s="9">
-        <v>0.0074906367041198503</v>
+        <v>0.005434782608695652</v>
       </c>
       <c r="AD24" s="6">
+        <v>69</v>
+      </c>
+      <c r="AE24" s="6">
         <v>53</v>
-      </c>
-      <c r="AE24" s="6">
-        <v>38</v>
       </c>
       <c r="AF24" s="6">
         <v>4</v>
       </c>
       <c r="AG24" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH24" s="6">
+        <v>20</v>
+      </c>
+      <c r="AI24" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="6">
+        <v>20</v>
+      </c>
+      <c r="AL24" s="6">
         <v>19</v>
-      </c>
-      <c r="AI24" s="6">
-        <v>3</v>
-      </c>
-      <c r="AJ24" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="6">
-        <v>16</v>
-      </c>
-      <c r="AL24" s="6">
-        <v>9</v>
       </c>
       <c r="AM24" s="6">
         <v>2</v>
@@ -5191,7 +5188,7 @@
         <v>1164</v>
       </c>
       <c r="O25" s="6">
-        <v>872</v>
+        <v>1080</v>
       </c>
       <c r="P25" s="7">
         <v>3.6357346483704975</v>
@@ -5209,37 +5206,37 @@
         <v>0.3972222222222222</v>
       </c>
       <c r="U25" s="9">
-        <v>0.18119266055045871</v>
+        <v>0.16944444444444445</v>
       </c>
       <c r="V25" s="9">
-        <v>0.0011467889908256881</v>
+        <v>0.00092592592592592596</v>
       </c>
       <c r="W25" s="9">
         <v>0</v>
       </c>
       <c r="X25" s="9">
-        <v>0.13876146788990826</v>
+        <v>0.13148148148148148</v>
       </c>
       <c r="Y25" s="9">
-        <v>0.024082568807339451</v>
+        <v>0.020370370370370372</v>
       </c>
       <c r="Z25" s="9">
-        <v>0.0045871559633027525</v>
+        <v>0.0037037037037037038</v>
       </c>
       <c r="AA25" s="9">
-        <v>0.048165137614678902</v>
+        <v>0.045370370370370373</v>
       </c>
       <c r="AB25" s="9">
-        <v>0.0057339449541284407</v>
+        <v>0.0046296296296296294</v>
       </c>
       <c r="AC25" s="9">
-        <v>0.014908256880733946</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="AD25" s="6">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="AE25" s="6">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="AF25" s="6">
         <v>1</v>
@@ -5248,22 +5245,22 @@
         <v>0</v>
       </c>
       <c r="AH25" s="6">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="AI25" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ25" s="6">
         <v>4</v>
       </c>
       <c r="AK25" s="6">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AL25" s="6">
         <v>5</v>
       </c>
       <c r="AM25" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN25" s="9">
         <v>0</v>
@@ -5625,7 +5622,7 @@
         <v>19580</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5656,49 +5653,49 @@
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="5">
-        <v>44581.261666666665</v>
+        <v>45684.409999999996</v>
       </c>
       <c r="N28" s="6">
-        <v>383</v>
+        <v>466</v>
       </c>
       <c r="O28" s="6">
-        <v>273</v>
+        <v>336</v>
       </c>
       <c r="P28" s="7">
-        <v>6.3780188775510203</v>
+        <v>8.3423670168067225</v>
       </c>
       <c r="Q28" s="8">
-        <v>21.448657142857144</v>
+        <v>24.475198511904761</v>
       </c>
       <c r="R28" s="8">
-        <v>8.3299490421455946</v>
+        <v>9.3327124223602489</v>
       </c>
       <c r="S28" s="8">
         <v>7</v>
       </c>
       <c r="T28" s="9">
-        <v>0.19413919413919414</v>
+        <v>0.17261904761904762</v>
       </c>
       <c r="U28" s="9">
-        <v>0.098901098901098897</v>
+        <v>0.089285714285714288</v>
       </c>
       <c r="V28" s="9">
         <v>0</v>
       </c>
       <c r="W28" s="9">
-        <v>0.0073260073260000003</v>
+        <v>0.0059523809519999998</v>
       </c>
       <c r="X28" s="9">
-        <v>0.047619047619047616</v>
+        <v>0.044642857142857144</v>
       </c>
       <c r="Y28" s="9">
-        <v>0.018315018315018316</v>
+        <v>0.017857142857142856</v>
       </c>
       <c r="Z28" s="9">
-        <v>0.003663003663003663</v>
+        <v>0.002976190476190476</v>
       </c>
       <c r="AA28" s="9">
-        <v>0.065934065934065936</v>
+        <v>0.059523809523809521</v>
       </c>
       <c r="AB28" s="9">
         <v>0</v>
@@ -5707,10 +5704,10 @@
         <v>0</v>
       </c>
       <c r="AD28" s="6">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AE28" s="6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF28" s="6">
         <v>0</v>
@@ -5719,16 +5716,16 @@
         <v>2</v>
       </c>
       <c r="AH28" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI28" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ28" s="6">
         <v>1</v>
       </c>
       <c r="AK28" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL28" s="6">
         <v>0</v>
@@ -5782,7 +5779,7 @@
         <v>19581</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C29" s="4">
         <v>51</v>
@@ -5813,70 +5810,70 @@
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="5">
-        <v>45318.746666666666</v>
+        <v>53114.82</v>
       </c>
       <c r="N29" s="6">
-        <v>392</v>
+        <v>541</v>
       </c>
       <c r="O29" s="6">
-        <v>306</v>
+        <v>419</v>
       </c>
       <c r="P29" s="7">
-        <v>5.0800002564102567</v>
+        <v>6.0313113970588228</v>
       </c>
       <c r="Q29" s="8">
-        <v>32.673958552631582</v>
+        <v>37.952369638554217</v>
       </c>
       <c r="R29" s="8">
-        <v>20.275675675675679</v>
+        <v>24.714567901234567</v>
       </c>
       <c r="S29" s="8">
         <v>8</v>
       </c>
       <c r="T29" s="9">
-        <v>0.072368421052631582</v>
+        <v>0.060240963855421686</v>
       </c>
       <c r="U29" s="9">
-        <v>0.14052287581699346</v>
+        <v>0.12649164677804295</v>
       </c>
       <c r="V29" s="9">
-        <v>0.019607843137254902</v>
+        <v>0.019093078758949882</v>
       </c>
       <c r="W29" s="9">
-        <v>0.003267973856</v>
+        <v>0.0047732696890000004</v>
       </c>
       <c r="X29" s="9">
-        <v>0.035947712418300651</v>
+        <v>0.031026252983293555</v>
       </c>
       <c r="Y29" s="9">
-        <v>0.0032679738562091504</v>
+        <v>0.0023866348448687352</v>
       </c>
       <c r="Z29" s="9">
         <v>0</v>
       </c>
       <c r="AA29" s="9">
-        <v>0.042483660130718956</v>
+        <v>0.038186157517899763</v>
       </c>
       <c r="AB29" s="9">
-        <v>0.0032679738562091504</v>
+        <v>0.0023866348448687352</v>
       </c>
       <c r="AC29" s="9">
-        <v>0.052287581699346407</v>
+        <v>0.042959427207637228</v>
       </c>
       <c r="AD29" s="6">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AE29" s="6">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="AF29" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG29" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH29" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI29" s="6">
         <v>1</v>
@@ -5885,13 +5882,13 @@
         <v>0</v>
       </c>
       <c r="AK29" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AL29" s="6">
         <v>1</v>
       </c>
       <c r="AM29" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN29" s="9">
         <v>0</v>
@@ -5988,7 +5985,7 @@
         <v>4.5740217391304352</v>
       </c>
       <c r="S30" s="8">
-        <v>8</v>
+        <v>6.2999999999999998</v>
       </c>
       <c r="T30" s="9">
         <v>0.38709677419354838</v>
@@ -6096,7 +6093,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>51</v>
@@ -6125,82 +6122,82 @@
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="5">
-        <v>43831.771666666667</v>
+        <v>46345.25</v>
       </c>
       <c r="N31" s="6">
-        <v>408</v>
+        <v>512</v>
       </c>
       <c r="O31" s="6">
-        <v>232</v>
+        <v>290</v>
       </c>
       <c r="P31" s="7">
-        <v>4.2604164999999998</v>
+        <v>3.9063364356435644</v>
       </c>
       <c r="Q31" s="8">
-        <v>19.969324999999998</v>
+        <v>19.410919655172414</v>
       </c>
       <c r="R31" s="8">
-        <v>8.4050209606986908</v>
+        <v>8.2962695804195796</v>
       </c>
       <c r="S31" s="8">
         <v>7</v>
       </c>
       <c r="T31" s="9">
-        <v>0.21551724137931033</v>
+        <v>0.22413793103448276</v>
       </c>
       <c r="U31" s="9">
-        <v>0.12931034482758622</v>
+        <v>0.14137931034482759</v>
       </c>
       <c r="V31" s="9">
-        <v>0.03017241379310345</v>
+        <v>0.027586206896551724</v>
       </c>
       <c r="W31" s="9">
         <v>0</v>
       </c>
       <c r="X31" s="9">
-        <v>0.060344827586206899</v>
+        <v>0.072413793103448282</v>
       </c>
       <c r="Y31" s="9">
-        <v>0.0043103448275862068</v>
+        <v>0.0068965517241379309</v>
       </c>
       <c r="Z31" s="9">
         <v>0</v>
       </c>
       <c r="AA31" s="9">
-        <v>0.012931034482758621</v>
+        <v>0.013793103448275862</v>
       </c>
       <c r="AB31" s="9">
-        <v>0.021551724137931036</v>
+        <v>0.034482758620689655</v>
       </c>
       <c r="AC31" s="9">
-        <v>0.017241379310344827</v>
+        <v>0.013793103448275862</v>
       </c>
       <c r="AD31" s="6">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="AE31" s="6">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="AF31" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG31" s="6">
         <v>0</v>
       </c>
       <c r="AH31" s="6">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AI31" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ31" s="6">
         <v>0</v>
       </c>
       <c r="AK31" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL31" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AM31" s="6">
         <v>4</v>
@@ -6718,7 +6715,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>51</v>
@@ -6749,70 +6746,70 @@
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="5">
-        <v>36878.554999999993</v>
+        <v>44406.529999999992</v>
       </c>
       <c r="N35" s="6">
-        <v>372</v>
+        <v>522</v>
       </c>
       <c r="O35" s="6">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="P35" s="7">
-        <v>3.0842489010989009</v>
+        <v>3.2424330724070449</v>
       </c>
       <c r="Q35" s="8">
-        <v>16.326200423728814</v>
+        <v>17.700593471810091</v>
       </c>
       <c r="R35" s="8">
-        <v>5.6557031111111113</v>
+        <v>6.7802653374233133</v>
       </c>
       <c r="S35" s="8">
         <v>8</v>
       </c>
       <c r="T35" s="9">
-        <v>0.52542372881355937</v>
+        <v>0.44213649851632048</v>
       </c>
       <c r="U35" s="9">
-        <v>0.28151260504201681</v>
+        <v>0.27728613569321536</v>
       </c>
       <c r="V35" s="9">
-        <v>0.025210084033613446</v>
+        <v>0.026548672566371681</v>
       </c>
       <c r="W35" s="9">
         <v>0</v>
       </c>
       <c r="X35" s="9">
-        <v>0.037815126050420166</v>
+        <v>0.035398230088495575</v>
       </c>
       <c r="Y35" s="9">
-        <v>0.0084033613445378148</v>
+        <v>0.0058997050147492625</v>
       </c>
       <c r="Z35" s="9">
-        <v>0.0042016806722689074</v>
+        <v>0.0029498525073746312</v>
       </c>
       <c r="AA35" s="9">
-        <v>0.11764705882352941</v>
+        <v>0.085545722713864306</v>
       </c>
       <c r="AB35" s="9">
-        <v>0.10084033613445378</v>
+        <v>0.10619469026548672</v>
       </c>
       <c r="AC35" s="9">
-        <v>0.033613445378151259</v>
+        <v>0.0471976401179941</v>
       </c>
       <c r="AD35" s="6">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="AE35" s="6">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="AF35" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG35" s="6">
         <v>0</v>
       </c>
       <c r="AH35" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI35" s="6">
         <v>2</v>
@@ -6821,13 +6818,13 @@
         <v>1</v>
       </c>
       <c r="AK35" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL35" s="6">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AM35" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AN35" s="9">
         <v>0</v>
@@ -7166,7 +7163,7 @@
         <v>431</v>
       </c>
       <c r="O38" s="6">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="P38" s="7">
         <v>2.6897737704918034</v>
@@ -7184,16 +7181,16 @@
         <v>0.7421875</v>
       </c>
       <c r="U38" s="9">
-        <v>0.052356020942408377</v>
+        <v>0.046875</v>
       </c>
       <c r="V38" s="9">
-        <v>0.015706806282722512</v>
+        <v>0.01171875</v>
       </c>
       <c r="W38" s="9">
         <v>0</v>
       </c>
       <c r="X38" s="9">
-        <v>0.026178010471204188</v>
+        <v>0.0234375</v>
       </c>
       <c r="Y38" s="9">
         <v>0</v>
@@ -7205,16 +7202,16 @@
         <v>0</v>
       </c>
       <c r="AB38" s="9">
-        <v>0</v>
+        <v>0.00390625</v>
       </c>
       <c r="AC38" s="9">
-        <v>0.010471204188481676</v>
+        <v>0.0078125</v>
       </c>
       <c r="AD38" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE38" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF38" s="6">
         <v>3</v>
@@ -7223,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="AH38" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI38" s="6">
         <v>0</v>
@@ -7235,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="AL38" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM38" s="6">
         <v>2</v>
@@ -7443,7 +7440,7 @@
         <v>19615</v>
       </c>
       <c r="B40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C40" s="4">
         <v>51</v>
@@ -7474,40 +7471,40 @@
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="5">
-        <v>39015.654999999999</v>
+        <v>41905.129999999997</v>
       </c>
       <c r="N40" s="6">
+        <v>509</v>
+      </c>
+      <c r="O40" s="6">
         <v>401</v>
       </c>
-      <c r="O40" s="6">
-        <v>309</v>
-      </c>
       <c r="P40" s="7">
-        <v>3.5638628504672898</v>
+        <v>3.5886334558823529</v>
       </c>
       <c r="Q40" s="8">
-        <v>20.086928104575165</v>
+        <v>19.266122361809046</v>
       </c>
       <c r="R40" s="8">
-        <v>9.8927152317880793</v>
+        <v>8.9503383248730977</v>
       </c>
       <c r="S40" s="8">
         <v>7</v>
       </c>
       <c r="T40" s="9">
-        <v>0.26470588235294118</v>
+        <v>0.30653266331658291</v>
       </c>
       <c r="U40" s="9">
-        <v>0.064724919093851127</v>
+        <v>0.057356608478802994</v>
       </c>
       <c r="V40" s="9">
-        <v>0.0032362459546925568</v>
+        <v>0.0049875311720698253</v>
       </c>
       <c r="W40" s="9">
         <v>0</v>
       </c>
       <c r="X40" s="9">
-        <v>0.035598705501618123</v>
+        <v>0.032418952618453865</v>
       </c>
       <c r="Y40" s="9">
         <v>0</v>
@@ -7516,28 +7513,28 @@
         <v>0</v>
       </c>
       <c r="AA40" s="9">
-        <v>0.016181229773462782</v>
+        <v>0.012468827930174564</v>
       </c>
       <c r="AB40" s="9">
-        <v>0.0097087378640776691</v>
+        <v>0.007481296758104738</v>
       </c>
       <c r="AC40" s="9">
-        <v>0.012944983818770227</v>
+        <v>0.0099750623441396506</v>
       </c>
       <c r="AD40" s="6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE40" s="6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF40" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG40" s="6">
         <v>0</v>
       </c>
       <c r="AH40" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI40" s="6">
         <v>0</v>
@@ -7816,7 +7813,7 @@
         <v>0.013297872340425532</v>
       </c>
       <c r="W42" s="9">
-        <v>0.0079787234040000002</v>
+        <v>0.010638297872</v>
       </c>
       <c r="X42" s="9">
         <v>0.018617021276595744</v>
@@ -7846,7 +7843,7 @@
         <v>5</v>
       </c>
       <c r="AG42" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH42" s="6">
         <v>7</v>
@@ -9141,7 +9138,7 @@
         <v>496</v>
       </c>
       <c r="O51" s="6">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="P51" s="7">
         <v>4.5237375757575764</v>
@@ -9159,16 +9156,16 @@
         <v>0.12109375</v>
       </c>
       <c r="U51" s="9">
-        <v>0.23195876288659795</v>
+        <v>0.1953125</v>
       </c>
       <c r="V51" s="9">
-        <v>0.061855670103092786</v>
+        <v>0.0546875</v>
       </c>
       <c r="W51" s="9">
-        <v>0.0051546391749999997</v>
+        <v>0.00390625</v>
       </c>
       <c r="X51" s="9">
-        <v>0.077319587628865982</v>
+        <v>0.0703125</v>
       </c>
       <c r="Y51" s="9">
         <v>0</v>
@@ -9177,28 +9174,28 @@
         <v>0</v>
       </c>
       <c r="AA51" s="9">
-        <v>0.010309278350515464</v>
+        <v>0.0078125</v>
       </c>
       <c r="AB51" s="9">
-        <v>0.041237113402061855</v>
+        <v>0.03125</v>
       </c>
       <c r="AC51" s="9">
-        <v>0.061855670103092786</v>
+        <v>0.046875</v>
       </c>
       <c r="AD51" s="6">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AE51" s="6">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF51" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG51" s="6">
         <v>1</v>
       </c>
       <c r="AH51" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AI51" s="6">
         <v>0</v>
@@ -9730,7 +9727,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9759,82 +9756,82 @@
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="5">
-        <v>49894.273333333324</v>
+        <v>56863.669999999998</v>
       </c>
       <c r="N55" s="6">
-        <v>478</v>
+        <v>648</v>
       </c>
       <c r="O55" s="6">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="P55" s="7">
-        <v>2.8212119047619044</v>
+        <v>2.7732693290734827</v>
       </c>
       <c r="Q55" s="8">
-        <v>16.334423831775702</v>
+        <v>15.886561267605634</v>
       </c>
       <c r="R55" s="8">
-        <v>5.9291868292682928</v>
+        <v>5.6407407407407408</v>
       </c>
       <c r="S55" s="8">
         <v>8</v>
       </c>
       <c r="T55" s="9">
-        <v>0.42523364485981308</v>
+        <v>0.46478873239436619</v>
       </c>
       <c r="U55" s="9">
-        <v>0.20093457943925233</v>
+        <v>0.20070422535211269</v>
       </c>
       <c r="V55" s="9">
-        <v>0.018691588785046728</v>
+        <v>0.02464788732394366</v>
       </c>
       <c r="W55" s="9">
-        <v>0.0046728971959999997</v>
+        <v>0.010563380281</v>
       </c>
       <c r="X55" s="9">
-        <v>0.10280373831775701</v>
+        <v>0.09154929577464789</v>
       </c>
       <c r="Y55" s="9">
-        <v>0.02336448598130841</v>
+        <v>0.031690140845070422</v>
       </c>
       <c r="Z55" s="9">
         <v>0</v>
       </c>
       <c r="AA55" s="9">
-        <v>0.079439252336448593</v>
+        <v>0.098591549295774641</v>
       </c>
       <c r="AB55" s="9">
-        <v>0.051401869158878503</v>
+        <v>0.042253521126760563</v>
       </c>
       <c r="AC55" s="9">
         <v>0</v>
       </c>
       <c r="AD55" s="6">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="AE55" s="6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="AF55" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG55" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH55" s="6">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI55" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AJ55" s="6">
         <v>0</v>
       </c>
       <c r="AK55" s="6">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AL55" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM55" s="6">
         <v>0</v>
@@ -9920,7 +9917,7 @@
         <v>1059</v>
       </c>
       <c r="O56" s="6">
-        <v>645</v>
+        <v>802</v>
       </c>
       <c r="P56" s="7">
         <v>6.3278353440150807</v>
@@ -9938,64 +9935,64 @@
         <v>0.29536921151439299</v>
       </c>
       <c r="U56" s="9">
-        <v>0.13643410852713178</v>
+        <v>0.12718204488778054</v>
       </c>
       <c r="V56" s="9">
-        <v>0.017054263565891473</v>
+        <v>0.019950124688279301</v>
       </c>
       <c r="W56" s="9">
-        <v>0.0031007751930000002</v>
+        <v>0.002493765586</v>
       </c>
       <c r="X56" s="9">
-        <v>0.093023255813953487</v>
+        <v>0.082294264339152115</v>
       </c>
       <c r="Y56" s="9">
-        <v>0.0031007751937984496</v>
+        <v>0.0024937655860349127</v>
       </c>
       <c r="Z56" s="9">
-        <v>0.0015503875968992248</v>
+        <v>0.0024937655860349127</v>
       </c>
       <c r="AA56" s="9">
-        <v>0.0062015503875968991</v>
+        <v>0.0062344139650872821</v>
       </c>
       <c r="AB56" s="9">
-        <v>0.0015503875968992248</v>
+        <v>0.0012468827930174563</v>
       </c>
       <c r="AC56" s="9">
-        <v>0.021705426356589147</v>
+        <v>0.019950124688279301</v>
       </c>
       <c r="AD56" s="6">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="AE56" s="6">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="AF56" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AG56" s="6">
         <v>2</v>
       </c>
       <c r="AH56" s="6">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AI56" s="6">
         <v>2</v>
       </c>
       <c r="AJ56" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK56" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL56" s="6">
         <v>1</v>
       </c>
       <c r="AM56" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AN56" s="9">
-        <v>0.010852713178294573</v>
+        <v>0.0087281795511221939</v>
       </c>
       <c r="AO56" s="6">
         <v>7</v>
@@ -10292,7 +10289,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>51</v>
@@ -10323,34 +10320,34 @@
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="5">
-        <v>26594.329999999998</v>
+        <v>28958.02</v>
       </c>
       <c r="N59" s="6">
-        <v>246</v>
+        <v>312</v>
       </c>
       <c r="O59" s="6">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="P59" s="7">
-        <v>5.5829922131147542</v>
+        <v>5.7990864516129026</v>
       </c>
       <c r="Q59" s="8">
-        <v>18.595832857142856</v>
+        <v>18.801904571428569</v>
       </c>
       <c r="R59" s="8">
-        <v>5.9440478571428574</v>
+        <v>5.9505714285714282</v>
       </c>
       <c r="S59" s="8">
         <v>7</v>
       </c>
       <c r="T59" s="9">
-        <v>0.18571428571428572</v>
+        <v>0.17714285714285713</v>
       </c>
       <c r="U59" s="9">
-        <v>0.18571428571428572</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="V59" s="9">
-        <v>0.014285714285714285</v>
+        <v>0.011428571428571429</v>
       </c>
       <c r="W59" s="9">
         <v>0</v>
@@ -10365,19 +10362,19 @@
         <v>0</v>
       </c>
       <c r="AA59" s="9">
-        <v>0.0071428571428571426</v>
+        <v>0.0057142857142857143</v>
       </c>
       <c r="AB59" s="9">
-        <v>0.10714285714285714</v>
+        <v>0.12571428571428572</v>
       </c>
       <c r="AC59" s="9">
         <v>0.057142857142857141</v>
       </c>
       <c r="AD59" s="6">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="AE59" s="6">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="AF59" s="6">
         <v>2</v>
@@ -10398,10 +10395,10 @@
         <v>1</v>
       </c>
       <c r="AL59" s="6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AM59" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN59" s="9">
         <v>0</v>
@@ -10581,7 +10578,7 @@
         <v>522</v>
       </c>
       <c r="O61" s="6">
-        <v>290</v>
+        <v>374</v>
       </c>
       <c r="P61" s="7">
         <v>3.6601817669172929</v>
@@ -10599,46 +10596,46 @@
         <v>0.55080213903743314</v>
       </c>
       <c r="U61" s="9">
-        <v>0.12758620689655173</v>
+        <v>0.11764705882352941</v>
       </c>
       <c r="V61" s="9">
-        <v>0.020689655172413793</v>
+        <v>0.021390374331550801</v>
       </c>
       <c r="W61" s="9">
-        <v>0.0068965517239999996</v>
+        <v>0.0053475935819999997</v>
       </c>
       <c r="X61" s="9">
-        <v>0.031034482758620689</v>
+        <v>0.029411764705882353</v>
       </c>
       <c r="Y61" s="9">
-        <v>0.010344827586206896</v>
+        <v>0.0080213903743315516</v>
       </c>
       <c r="Z61" s="9">
         <v>0</v>
       </c>
       <c r="AA61" s="9">
-        <v>0.055172413793103448</v>
+        <v>0.042780748663101602</v>
       </c>
       <c r="AB61" s="9">
-        <v>0.0068965517241379309</v>
+        <v>0.0053475935828877002</v>
       </c>
       <c r="AC61" s="9">
         <v>0</v>
       </c>
       <c r="AD61" s="6">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AE61" s="6">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AF61" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG61" s="6">
         <v>2</v>
       </c>
       <c r="AH61" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI61" s="6">
         <v>3</v>
@@ -10656,10 +10653,10 @@
         <v>0</v>
       </c>
       <c r="AN61" s="9">
-        <v>0.024137931034482758</v>
+        <v>0.032085561497326207</v>
       </c>
       <c r="AO61" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c t="s" r="AP61" s="4">
         <v>58</v>
@@ -11426,7 +11423,7 @@
         <v>19685</v>
       </c>
       <c r="B67" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="s" r="C67" s="4">
         <v>51</v>
@@ -11457,28 +11454,28 @@
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="5">
-        <v>23209.375</v>
+        <v>32449.449999999993</v>
       </c>
       <c r="N67" s="6">
-        <v>61</v>
+        <v>331</v>
       </c>
       <c r="O67" s="6">
         <v>44</v>
       </c>
       <c r="P67" s="7">
-        <v>8.3833338709677427</v>
+        <v>7.2280076923076928</v>
       </c>
       <c r="Q67" s="8">
-        <v>19.87575681818182</v>
+        <v>24.46277012987013</v>
       </c>
       <c r="R67" s="8">
-        <v>6.604166666666667</v>
+        <v>13.152295918367347</v>
       </c>
       <c r="S67" s="8">
         <v>7</v>
       </c>
       <c r="T67" s="9">
-        <v>0.31818181818181818</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="U67" s="9">
         <v>0.38636363636363635</v>
@@ -12318,7 +12315,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>51</v>
@@ -12349,40 +12346,40 @@
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5">
-        <v>38253.01666666667</v>
+        <v>40742.260000000002</v>
       </c>
       <c r="N73" s="6">
-        <v>353</v>
+        <v>439</v>
       </c>
       <c r="O73" s="6">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="P73" s="7">
-        <v>13.176217415730337</v>
+        <v>12.275075565610861</v>
       </c>
       <c r="Q73" s="8">
-        <v>42.992708482142859</v>
+        <v>40.205575444839859</v>
       </c>
       <c r="R73" s="8">
-        <v>24.204128828828829</v>
+        <v>22.372382310469316</v>
       </c>
       <c r="S73" s="8">
         <v>7</v>
       </c>
       <c r="T73" s="9">
-        <v>0.075892857142857137</v>
+        <v>0.064056939501779361</v>
       </c>
       <c r="U73" s="9">
-        <v>0.22077922077922077</v>
+        <v>0.21527777777777779</v>
       </c>
       <c r="V73" s="9">
-        <v>0.060606060606060608</v>
+        <v>0.059027777777777776</v>
       </c>
       <c r="W73" s="9">
         <v>0</v>
       </c>
       <c r="X73" s="9">
-        <v>0.012987012987012988</v>
+        <v>0.010416666666666666</v>
       </c>
       <c r="Y73" s="9">
         <v>0</v>
@@ -12391,22 +12388,22 @@
         <v>0</v>
       </c>
       <c r="AA73" s="9">
-        <v>0.017316017316017316</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="AB73" s="9">
-        <v>0.008658008658008658</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="AC73" s="9">
-        <v>0.14285714285714285</v>
+        <v>0.13194444444444445</v>
       </c>
       <c r="AD73" s="6">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AE73" s="6">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="AF73" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG73" s="6">
         <v>0</v>
@@ -12421,13 +12418,13 @@
         <v>0</v>
       </c>
       <c r="AK73" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL73" s="6">
         <v>4</v>
       </c>
-      <c r="AL73" s="6">
-        <v>2</v>
-      </c>
       <c r="AM73" s="6">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AN73" s="9">
         <v>0</v>
@@ -12789,7 +12786,7 @@
         <v>19706</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12818,7 +12815,7 @@
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="5">
-        <v>37180.056666666671</v>
+        <v>31868.620000000003</v>
       </c>
       <c r="N76" s="6">
         <v>352</v>
@@ -12911,7 +12908,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR76" s="4">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c t="s" r="AS76" s="4">
         <v>60</v>
@@ -12953,7 +12950,7 @@
         <v>155</v>
       </c>
       <c t="s" r="E77" s="4">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="F77" s="4">
         <v>54</v>
@@ -13167,7 +13164,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR78" s="4">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="AS78" s="4">
         <v>60</v>
@@ -13324,7 +13321,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR79" s="4">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="AS79" s="4">
         <v>60</v>
@@ -13479,7 +13476,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR80" s="4">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="AS80" s="4">
         <v>60</v>
@@ -13578,7 +13575,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR81" s="4">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="AS81" s="4">
         <v>60</v>
@@ -13620,7 +13617,7 @@
         <v>106</v>
       </c>
       <c t="s" r="E82" s="4">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="F82" s="4">
         <v>54</v>
@@ -14047,7 +14044,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR84" s="4">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="AS84" s="4">
         <v>60</v>
@@ -14460,7 +14457,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR87" s="4">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c t="s" r="AS87" s="4">
         <v>60</v>
@@ -14493,14 +14490,14 @@
         <v>19730</v>
       </c>
       <c r="B88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C88" s="4">
         <v>51</v>
       </c>
       <c r="D88" s="4"/>
       <c t="s" r="E88" s="4">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="F88" s="4">
         <v>54</v>
@@ -14522,70 +14519,70 @@
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="5">
-        <v>58126.89166666667</v>
+        <v>64593.040000000001</v>
       </c>
       <c r="N88" s="6">
-        <v>484</v>
+        <v>640</v>
       </c>
       <c r="O88" s="6">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="P88" s="7">
-        <v>7.5410701431492839</v>
+        <v>8.0618086821705432</v>
       </c>
       <c r="Q88" s="8">
-        <v>24.697185714285713</v>
+        <v>25.700509693877549</v>
       </c>
       <c r="R88" s="8">
-        <v>9.3876908496732039</v>
+        <v>10.039658461538462</v>
       </c>
       <c r="S88" s="8">
         <v>8</v>
       </c>
       <c r="T88" s="9">
-        <v>0.16233766233766234</v>
+        <v>0.12755102040816327</v>
       </c>
       <c r="U88" s="9">
-        <v>0.26213592233009708</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="V88" s="9">
-        <v>0.029126213592233011</v>
+        <v>0.030612244897959183</v>
       </c>
       <c r="W88" s="9">
-        <v>0.0097087378640000003</v>
+        <v>0.0051020408159999997</v>
       </c>
       <c r="X88" s="9">
-        <v>0.048543689320388349</v>
+        <v>0.030612244897959183</v>
       </c>
       <c r="Y88" s="9">
         <v>0</v>
       </c>
       <c r="Z88" s="9">
-        <v>0.0097087378640776691</v>
+        <v>0.0051020408163265302</v>
       </c>
       <c r="AA88" s="9">
-        <v>0.0097087378640776691</v>
+        <v>0.0051020408163265302</v>
       </c>
       <c r="AB88" s="9">
-        <v>0.067961165048543687</v>
+        <v>0.051020408163265307</v>
       </c>
       <c r="AC88" s="9">
-        <v>0.13592233009708737</v>
+        <v>0.18367346938775511</v>
       </c>
       <c r="AD88" s="6">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="AE88" s="6">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="AF88" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG88" s="6">
         <v>1</v>
       </c>
       <c r="AH88" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI88" s="6">
         <v>0</v>
@@ -14597,10 +14594,10 @@
         <v>1</v>
       </c>
       <c r="AL88" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM88" s="6">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AN88" s="9">
         <v>0</v>
@@ -14615,7 +14612,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR88" s="4">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="AS88" s="4">
         <v>60</v>
@@ -14657,7 +14654,7 @@
         <v>155</v>
       </c>
       <c t="s" r="E89" s="4">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c t="s" r="F89" s="4">
         <v>54</v>
@@ -14714,7 +14711,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR89" s="4">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c t="s" r="AS89" s="4">
         <v>60</v>
@@ -14871,7 +14868,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR90" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="AS90" s="4">
         <v>60</v>
@@ -14911,7 +14908,7 @@
       </c>
       <c r="D91" s="4"/>
       <c t="s" r="E91" s="4">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c t="s" r="F91" s="4">
         <v>54</v>
@@ -15026,7 +15023,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR91" s="4">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="AS91" s="4">
         <v>60</v>
@@ -15066,7 +15063,7 @@
       </c>
       <c r="D92" s="4"/>
       <c t="s" r="E92" s="4">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c t="s" r="F92" s="4">
         <v>54</v>
@@ -15112,13 +15109,13 @@
         <v>0.60802469135802473</v>
       </c>
       <c r="U92" s="9">
-        <v>0.27469135802469136</v>
+        <v>0.27777777777777779</v>
       </c>
       <c r="V92" s="9">
         <v>0.037037037037037035</v>
       </c>
       <c r="W92" s="9">
-        <v>0.003086419753</v>
+        <v>0.0092592592590000009</v>
       </c>
       <c r="X92" s="9">
         <v>0.058641975308641972</v>
@@ -15142,13 +15139,13 @@
         <v>100</v>
       </c>
       <c r="AE92" s="6">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AF92" s="6">
         <v>12</v>
       </c>
       <c r="AG92" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH92" s="6">
         <v>19</v>
@@ -15338,7 +15335,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR93" s="4">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="AS93" s="4">
         <v>60</v>
@@ -15380,7 +15377,7 @@
         <v>132</v>
       </c>
       <c t="s" r="E94" s="4">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="F94" s="4">
         <v>54</v>
@@ -15495,7 +15492,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR94" s="4">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="AS94" s="4">
         <v>60</v>
@@ -15535,7 +15532,7 @@
       </c>
       <c r="D95" s="4"/>
       <c t="s" r="E95" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="F95" s="4">
         <v>54</v>
@@ -15650,7 +15647,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR95" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="AS95" s="4">
         <v>60</v>
@@ -15692,7 +15689,7 @@
         <v>52</v>
       </c>
       <c t="s" r="E96" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="F96" s="4">
         <v>54</v>
@@ -15807,7 +15804,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR96" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c t="s" r="AS96" s="4">
         <v>60</v>
@@ -15847,7 +15844,7 @@
       </c>
       <c r="D97" s="4"/>
       <c t="s" r="E97" s="4">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="F97" s="4">
         <v>54</v>
@@ -15962,7 +15959,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR97" s="4">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="AS97" s="4">
         <v>60</v>
@@ -16002,7 +15999,7 @@
       </c>
       <c r="D98" s="4"/>
       <c t="s" r="E98" s="4">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="F98" s="4">
         <v>54</v>
@@ -16117,7 +16114,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR98" s="4">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="AS98" s="4">
         <v>60</v>
@@ -16187,7 +16184,7 @@
         <v>571</v>
       </c>
       <c r="O99" s="6">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="P99" s="7">
         <v>4.1004391915641474</v>
@@ -16205,16 +16202,16 @@
         <v>0.52142857142857146</v>
       </c>
       <c r="U99" s="9">
-        <v>0.1891891891891892</v>
+        <v>0.18928571428571428</v>
       </c>
       <c r="V99" s="9">
-        <v>0.013513513513513514</v>
+        <v>0.010714285714285714</v>
       </c>
       <c r="W99" s="9">
-        <v>0.0090090090090000005</v>
+        <v>0.010714285714</v>
       </c>
       <c r="X99" s="9">
-        <v>0.013513513513513514</v>
+        <v>0.010714285714285714</v>
       </c>
       <c r="Y99" s="9">
         <v>0</v>
@@ -16223,25 +16220,25 @@
         <v>0</v>
       </c>
       <c r="AA99" s="9">
-        <v>0.063063063063063057</v>
+        <v>0.067857142857142852</v>
       </c>
       <c r="AB99" s="9">
-        <v>0.040540540540540543</v>
+        <v>0.042857142857142858</v>
       </c>
       <c r="AC99" s="9">
-        <v>0.063063063063063057</v>
+        <v>0.057142857142857141</v>
       </c>
       <c r="AD99" s="6">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="AE99" s="6">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AF99" s="6">
         <v>3</v>
       </c>
       <c r="AG99" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH99" s="6">
         <v>3</v>
@@ -16253,13 +16250,13 @@
         <v>0</v>
       </c>
       <c r="AK99" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AL99" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AM99" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AN99" s="9">
         <v>0</v>
@@ -16274,7 +16271,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR99" s="4">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c t="s" r="AS99" s="4">
         <v>60</v>
@@ -16676,13 +16673,13 @@
         <v>0.29209621993127149</v>
       </c>
       <c r="U102" s="9">
-        <v>0.10884353741496598</v>
+        <v>0.11224489795918367</v>
       </c>
       <c r="V102" s="9">
         <v>0.017006802721088437</v>
       </c>
       <c r="W102" s="9">
-        <v>0.003401360544</v>
+        <v>0.0068027210879999999</v>
       </c>
       <c r="X102" s="9">
         <v>0.030612244897959183</v>
@@ -16706,13 +16703,13 @@
         <v>49</v>
       </c>
       <c r="AE102" s="6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF102" s="6">
         <v>5</v>
       </c>
       <c r="AG102" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH102" s="6">
         <v>9</v>
@@ -16787,7 +16784,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E103" s="4">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="F103" s="4">
         <v>54</v>
@@ -16902,7 +16899,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR103" s="4">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c t="s" r="AS103" s="4">
         <v>60</v>
@@ -16944,7 +16941,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E104" s="4">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="F104" s="4">
         <v>54</v>
@@ -17059,7 +17056,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR104" s="4">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c t="s" r="AS104" s="4">
         <v>60</v>
@@ -17098,10 +17095,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D105" s="4">
+        <v>194</v>
+      </c>
+      <c t="s" r="E105" s="4">
         <v>195</v>
-      </c>
-      <c t="s" r="E105" s="4">
-        <v>196</v>
       </c>
       <c t="s" r="F105" s="4">
         <v>54</v>
@@ -17119,7 +17116,7 @@
         <v>54</v>
       </c>
       <c t="s" r="K105" s="4">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="5">
@@ -17210,13 +17207,13 @@
         <v>0</v>
       </c>
       <c t="s" r="AP105" s="4">
+        <v>196</v>
+      </c>
+      <c t="s" r="AQ105" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR105" s="4">
         <v>197</v>
-      </c>
-      <c t="s" r="AQ105" s="4">
-        <v>59</v>
-      </c>
-      <c t="s" r="AR105" s="4">
-        <v>198</v>
       </c>
       <c t="s" r="AS105" s="4">
         <v>60</v>
@@ -17373,7 +17370,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR106" s="4">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="AS106" s="4">
         <v>60</v>
@@ -17461,13 +17458,13 @@
         <v>0.40993788819875776</v>
       </c>
       <c r="U107" s="9">
-        <v>0.41614906832298137</v>
+        <v>0.42236024844720499</v>
       </c>
       <c r="V107" s="9">
         <v>0.012422360248447204</v>
       </c>
       <c r="W107" s="9">
-        <v>0.0062111801239999997</v>
+        <v>0.018633540372000001</v>
       </c>
       <c r="X107" s="9">
         <v>0.16149068322981366</v>
@@ -17491,13 +17488,13 @@
         <v>88</v>
       </c>
       <c r="AE107" s="6">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF107" s="6">
         <v>2</v>
       </c>
       <c r="AG107" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH107" s="6">
         <v>26</v>
@@ -17572,7 +17569,7 @@
         <v>77</v>
       </c>
       <c t="s" r="E108" s="4">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="F108" s="4">
         <v>54</v>
@@ -17687,7 +17684,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR108" s="4">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="AS108" s="4">
         <v>60</v>
@@ -17844,7 +17841,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR109" s="4">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c t="s" r="AS109" s="4">
         <v>60</v>
@@ -17886,7 +17883,7 @@
         <v>101</v>
       </c>
       <c t="s" r="E110" s="4">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c t="s" r="F110" s="4">
         <v>54</v>
@@ -18001,7 +17998,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR110" s="4">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c t="s" r="AS110" s="4">
         <v>60</v>
@@ -18043,7 +18040,7 @@
         <v>132</v>
       </c>
       <c t="s" r="E111" s="4">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c t="s" r="F111" s="4">
         <v>54</v>
@@ -18158,7 +18155,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR111" s="4">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="AS111" s="4">
         <v>60</v>
@@ -18200,7 +18197,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E112" s="4">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="F112" s="4">
         <v>54</v>
@@ -18354,10 +18351,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D113" s="4">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="E113" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="F113" s="4">
         <v>54</v>
@@ -18403,13 +18400,13 @@
         <v>0.3742690058479532</v>
       </c>
       <c r="U113" s="9">
-        <v>0.34502923976608185</v>
+        <v>0.35087719298245612</v>
       </c>
       <c r="V113" s="9">
         <v>0.017543859649122806</v>
       </c>
       <c r="W113" s="9">
-        <v>0</v>
+        <v>0.017543859649000001</v>
       </c>
       <c r="X113" s="9">
         <v>0.0058479532163742687</v>
@@ -18433,13 +18430,13 @@
         <v>64</v>
       </c>
       <c r="AE113" s="6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF113" s="6">
         <v>3</v>
       </c>
       <c r="AG113" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH113" s="6">
         <v>1</v>
@@ -18472,7 +18469,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR113" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="AS113" s="4">
         <v>60</v>
@@ -18512,7 +18509,7 @@
       </c>
       <c r="D114" s="4"/>
       <c t="s" r="E114" s="4">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c t="s" r="F114" s="4">
         <v>54</v>
@@ -18627,7 +18624,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR114" s="4">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="AS114" s="4">
         <v>60</v>
@@ -18870,13 +18867,13 @@
         <v>0.80341880341880345</v>
       </c>
       <c r="U116" s="9">
-        <v>0.20085470085470086</v>
+        <v>0.21367521367521367</v>
       </c>
       <c r="V116" s="9">
         <v>0.017094017094017096</v>
       </c>
       <c r="W116" s="9">
-        <v>0.047008547008000001</v>
+        <v>0.12820512820499999</v>
       </c>
       <c r="X116" s="9">
         <v>0.059829059829059832</v>
@@ -18900,13 +18897,13 @@
         <v>70</v>
       </c>
       <c r="AE116" s="6">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AF116" s="6">
         <v>4</v>
       </c>
       <c r="AG116" s="6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AH116" s="6">
         <v>14</v>
@@ -18978,10 +18975,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D117" s="4">
+        <v>209</v>
+      </c>
+      <c t="s" r="E117" s="4">
         <v>210</v>
-      </c>
-      <c t="s" r="E117" s="4">
-        <v>211</v>
       </c>
       <c t="s" r="F117" s="4">
         <v>54</v>
@@ -19078,7 +19075,7 @@
       </c>
       <c r="D118" s="4"/>
       <c t="s" r="E118" s="4">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="F118" s="4">
         <v>54</v>
@@ -19193,7 +19190,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR118" s="4">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="AS118" s="4">
         <v>60</v>
@@ -19233,7 +19230,7 @@
       </c>
       <c r="D119" s="4"/>
       <c t="s" r="E119" s="4">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="F119" s="4">
         <v>54</v>
@@ -19261,7 +19258,7 @@
         <v>646</v>
       </c>
       <c r="O119" s="6">
-        <v>299</v>
+        <v>384</v>
       </c>
       <c r="P119" s="7">
         <v>10.799091277258567</v>
@@ -19279,37 +19276,37 @@
         <v>0.125</v>
       </c>
       <c r="U119" s="9">
-        <v>0.15050167224080269</v>
+        <v>0.14322916666666666</v>
       </c>
       <c r="V119" s="9">
-        <v>0.0033444816053511705</v>
+        <v>0.0026041666666666665</v>
       </c>
       <c r="W119" s="9">
         <v>0</v>
       </c>
       <c r="X119" s="9">
-        <v>0.03678929765886288</v>
+        <v>0.028645833333333332</v>
       </c>
       <c r="Y119" s="9">
-        <v>0.010033444816053512</v>
+        <v>0.0078125</v>
       </c>
       <c r="Z119" s="9">
-        <v>0.0033444816053511705</v>
+        <v>0.0026041666666666665</v>
       </c>
       <c r="AA119" s="9">
-        <v>0.060200668896321072</v>
+        <v>0.059895833333333336</v>
       </c>
       <c r="AB119" s="9">
-        <v>0.046822742474916385</v>
+        <v>0.0390625</v>
       </c>
       <c r="AC119" s="9">
-        <v>0.040133779264214048</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="AD119" s="6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AE119" s="6">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AF119" s="6">
         <v>1</v>
@@ -19327,13 +19324,13 @@
         <v>1</v>
       </c>
       <c r="AK119" s="6">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AL119" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM119" s="6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AN119" s="9">
         <v>0</v>
@@ -19348,7 +19345,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR119" s="4">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="AS119" s="4">
         <v>60</v>
@@ -19390,7 +19387,7 @@
         <v>93</v>
       </c>
       <c t="s" r="E120" s="4">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="F120" s="4">
         <v>54</v>
@@ -19505,7 +19502,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR120" s="4">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="AS120" s="4">
         <v>60</v>
@@ -19732,7 +19729,7 @@
         <v>327</v>
       </c>
       <c r="O122" s="6">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="P122" s="7">
         <v>6.9713417682926835</v>
@@ -19750,46 +19747,46 @@
         <v>0.19587628865979381</v>
       </c>
       <c r="U122" s="9">
-        <v>0.21518987341772153</v>
+        <v>0.20408163265306123</v>
       </c>
       <c r="V122" s="9">
-        <v>0.0063291139240506328</v>
+        <v>0.01020408163265306</v>
       </c>
       <c r="W122" s="9">
         <v>0</v>
       </c>
       <c r="X122" s="9">
-        <v>0.088607594936708861</v>
+        <v>0.081632653061224483</v>
       </c>
       <c r="Y122" s="9">
-        <v>0.012658227848101266</v>
+        <v>0.01020408163265306</v>
       </c>
       <c r="Z122" s="9">
-        <v>0.0063291139240506328</v>
+        <v>0.0051020408163265302</v>
       </c>
       <c r="AA122" s="9">
-        <v>0.063291139240506333</v>
+        <v>0.071428571428571425</v>
       </c>
       <c r="AB122" s="9">
-        <v>0.018987341772151899</v>
+        <v>0.015306122448979591</v>
       </c>
       <c r="AC122" s="9">
-        <v>0.063291139240506333</v>
+        <v>0.051020408163265307</v>
       </c>
       <c r="AD122" s="6">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="AE122" s="6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF122" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG122" s="6">
         <v>0</v>
       </c>
       <c r="AH122" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI122" s="6">
         <v>2</v>
@@ -19798,7 +19795,7 @@
         <v>1</v>
       </c>
       <c r="AK122" s="6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL122" s="6">
         <v>3</v>
@@ -19859,7 +19856,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E123" s="4">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="F123" s="4">
         <v>54</v>
@@ -19887,7 +19884,7 @@
         <v>316</v>
       </c>
       <c r="O123" s="6">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="P123" s="7">
         <v>4.9440319354838707</v>
@@ -19905,16 +19902,16 @@
         <v>0.65779467680608361</v>
       </c>
       <c r="U123" s="9">
-        <v>0.058536585365853662</v>
+        <v>0.064638783269961975</v>
       </c>
       <c r="V123" s="9">
-        <v>0.0097560975609756097</v>
+        <v>0.0076045627376425855</v>
       </c>
       <c r="W123" s="9">
         <v>0</v>
       </c>
       <c r="X123" s="9">
-        <v>0.019512195121951219</v>
+        <v>0.026615969581749048</v>
       </c>
       <c r="Y123" s="9">
         <v>0</v>
@@ -19923,19 +19920,19 @@
         <v>0</v>
       </c>
       <c r="AA123" s="9">
-        <v>0.029268292682926831</v>
+        <v>0.034220532319391636</v>
       </c>
       <c r="AB123" s="9">
-        <v>0.0048780487804878049</v>
+        <v>0.0038022813688212928</v>
       </c>
       <c r="AC123" s="9">
         <v>0</v>
       </c>
       <c r="AD123" s="6">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AE123" s="6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AF123" s="6">
         <v>2</v>
@@ -19944,7 +19941,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI123" s="6">
         <v>0</v>
@@ -19953,7 +19950,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL123" s="6">
         <v>1</v>
@@ -19974,7 +19971,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR123" s="4">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="AS123" s="4">
         <v>60</v>
@@ -20016,7 +20013,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E124" s="4">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="F124" s="4">
         <v>54</v>
@@ -20131,7 +20128,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR124" s="4">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="AS124" s="4">
         <v>60</v>
@@ -20173,7 +20170,7 @@
         <v>75</v>
       </c>
       <c t="s" r="E125" s="4">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="F125" s="4">
         <v>54</v>
@@ -20327,10 +20324,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D126" s="4">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="E126" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="F126" s="4">
         <v>54</v>
@@ -20387,7 +20384,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR126" s="4">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="AS126" s="4">
         <v>60</v>
@@ -20457,7 +20454,7 @@
         <v>320</v>
       </c>
       <c r="O127" s="6">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="P127" s="7">
         <v>6.2307856687898084</v>
@@ -20475,16 +20472,16 @@
         <v>0.35684647302904565</v>
       </c>
       <c r="U127" s="9">
-        <v>0.13978494623655913</v>
+        <v>0.11618257261410789</v>
       </c>
       <c r="V127" s="9">
-        <v>0.010752688172043012</v>
+        <v>0.012448132780082987</v>
       </c>
       <c r="W127" s="9">
         <v>0</v>
       </c>
       <c r="X127" s="9">
-        <v>0.021505376344086023</v>
+        <v>0.020746887966804978</v>
       </c>
       <c r="Y127" s="9">
         <v>0</v>
@@ -20493,28 +20490,28 @@
         <v>0</v>
       </c>
       <c r="AA127" s="9">
-        <v>0.059139784946236562</v>
+        <v>0.045643153526970952</v>
       </c>
       <c r="AB127" s="9">
-        <v>0.0053763440860215058</v>
+        <v>0.0041493775933609959</v>
       </c>
       <c r="AC127" s="9">
-        <v>0.043010752688172046</v>
+        <v>0.033195020746887967</v>
       </c>
       <c r="AD127" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE127" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF127" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG127" s="6">
         <v>0</v>
       </c>
       <c r="AH127" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI127" s="6">
         <v>0</v>
@@ -20544,7 +20541,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR127" s="4">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="AS127" s="4">
         <v>60</v>
@@ -20701,7 +20698,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR128" s="4">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="AS128" s="4">
         <v>60</v>
@@ -20734,7 +20731,7 @@
         <v>19863</v>
       </c>
       <c r="B129" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="s" r="C129" s="4">
         <v>51</v>
@@ -20765,61 +20762,61 @@
       </c>
       <c r="L129" s="4"/>
       <c r="M129" s="5">
-        <v>35870.099999999991</v>
+        <v>45727.336666666662</v>
       </c>
       <c r="N129" s="6">
-        <v>225</v>
+        <v>435</v>
       </c>
       <c r="O129" s="6">
-        <v>112</v>
+        <v>309</v>
       </c>
       <c r="P129" s="7">
-        <v>4.9733739837398376</v>
+        <v>5.1910765486725658</v>
       </c>
       <c r="Q129" s="8">
-        <v>15.62177125</v>
+        <v>16.930890553745929</v>
       </c>
       <c r="R129" s="8">
-        <v>4.5002378571428574</v>
+        <v>5.3286568345323744</v>
       </c>
       <c r="S129" s="8">
         <v>7</v>
       </c>
       <c r="T129" s="9">
-        <v>0.48749999999999999</v>
+        <v>0.42671009771986973</v>
       </c>
       <c r="U129" s="9">
-        <v>0.089285714285714288</v>
+        <v>0.16181229773462782</v>
       </c>
       <c r="V129" s="9">
-        <v>0.026785714285714284</v>
+        <v>0.0097087378640776691</v>
       </c>
       <c r="W129" s="9">
         <v>0</v>
       </c>
       <c r="X129" s="9">
-        <v>0.026785714285714284</v>
+        <v>0.058252427184466021</v>
       </c>
       <c r="Y129" s="9">
-        <v>0.0089285714285714281</v>
+        <v>0.035598705501618123</v>
       </c>
       <c r="Z129" s="9">
         <v>0</v>
       </c>
       <c r="AA129" s="9">
-        <v>0.035714285714285712</v>
+        <v>0.11650485436893204</v>
       </c>
       <c r="AB129" s="9">
-        <v>0.017857142857142856</v>
+        <v>0.012944983818770227</v>
       </c>
       <c r="AC129" s="9">
-        <v>0</v>
+        <v>0.012944983818770227</v>
       </c>
       <c r="AD129" s="6">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="AE129" s="6">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AF129" s="6">
         <v>3</v>
@@ -20828,22 +20825,22 @@
         <v>0</v>
       </c>
       <c r="AH129" s="6">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AI129" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AJ129" s="6">
         <v>0</v>
       </c>
       <c r="AK129" s="6">
+        <v>36</v>
+      </c>
+      <c r="AL129" s="6">
         <v>4</v>
       </c>
-      <c r="AL129" s="6">
-        <v>2</v>
-      </c>
       <c r="AM129" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN129" s="9">
         <v>0</v>
@@ -20896,7 +20893,7 @@
       </c>
       <c r="D130" s="4"/>
       <c t="s" r="E130" s="4">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="F130" s="4">
         <v>54</v>
@@ -21048,10 +21045,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D131" s="4">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c t="s" r="E131" s="4">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c t="s" r="F131" s="4">
         <v>54</v>
@@ -21114,7 +21111,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR131" s="4">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="AS131" s="4">
         <v>60</v>
@@ -21147,7 +21144,7 @@
         <v>19872</v>
       </c>
       <c r="B132" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C132" s="4">
         <v>51</v>
@@ -21156,7 +21153,7 @@
         <v>101</v>
       </c>
       <c t="s" r="E132" s="4">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c t="s" r="F132" s="4">
         <v>54</v>
@@ -21178,40 +21175,40 @@
       </c>
       <c r="L132" s="4"/>
       <c r="M132" s="5">
-        <v>31445.563333333335</v>
+        <v>36200.630000000005</v>
       </c>
       <c r="N132" s="6">
-        <v>281</v>
+        <v>369</v>
       </c>
       <c r="O132" s="6">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="P132" s="7">
-        <v>8.9785988636363641</v>
+        <v>8.6889213872832372</v>
       </c>
       <c r="Q132" s="8">
-        <v>23.308139534883722</v>
+        <v>23.243254166666667</v>
       </c>
       <c r="R132" s="8">
-        <v>5.8777772357723572</v>
+        <v>6.0139913580246915</v>
       </c>
       <c r="S132" s="8">
         <v>8</v>
       </c>
       <c r="T132" s="9">
-        <v>0.077519379844961239</v>
+        <v>0.065476190476190479</v>
       </c>
       <c r="U132" s="9">
-        <v>0.14728682170542637</v>
+        <v>0.16071428571428573</v>
       </c>
       <c r="V132" s="9">
-        <v>0.03875968992248062</v>
+        <v>0.035714285714285712</v>
       </c>
       <c r="W132" s="9">
-        <v>0.0077519379839999999</v>
+        <v>0.0059523809519999998</v>
       </c>
       <c r="X132" s="9">
-        <v>0.0077519379844961239</v>
+        <v>0.0059523809523809521</v>
       </c>
       <c r="Y132" s="9">
         <v>0</v>
@@ -21220,22 +21217,22 @@
         <v>0</v>
       </c>
       <c r="AA132" s="9">
-        <v>0.054263565891472867</v>
+        <v>0.047619047619047616</v>
       </c>
       <c r="AB132" s="9">
-        <v>0.015503875968992248</v>
+        <v>0.017857142857142856</v>
       </c>
       <c r="AC132" s="9">
-        <v>0.046511627906976744</v>
+        <v>0.071428571428571425</v>
       </c>
       <c r="AD132" s="6">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AE132" s="6">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AF132" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG132" s="6">
         <v>1</v>
@@ -21250,13 +21247,13 @@
         <v>0</v>
       </c>
       <c r="AK132" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL132" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM132" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AN132" s="9">
         <v>0</v>
@@ -21271,7 +21268,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR132" s="4">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="AS132" s="4">
         <v>60</v>
@@ -21516,13 +21513,13 @@
         <v>0.14950166112956811</v>
       </c>
       <c r="U134" s="9">
-        <v>0.2814569536423841</v>
+        <v>0.28476821192052981</v>
       </c>
       <c r="V134" s="9">
         <v>0.016556291390728478</v>
       </c>
       <c r="W134" s="9">
-        <v>0.0033112582779999998</v>
+        <v>0.0099337748340000004</v>
       </c>
       <c r="X134" s="9">
         <v>0.013245033112582781</v>
@@ -21546,13 +21543,13 @@
         <v>90</v>
       </c>
       <c r="AE134" s="6">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF134" s="6">
         <v>5</v>
       </c>
       <c r="AG134" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH134" s="6">
         <v>4</v>
@@ -21585,7 +21582,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR134" s="4">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="AS134" s="4">
         <v>60</v>
@@ -21624,10 +21621,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D135" s="4">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="E135" s="4">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="F135" s="4">
         <v>54</v>
@@ -21742,7 +21739,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR135" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="AS135" s="4">
         <v>60</v>
@@ -21784,7 +21781,7 @@
         <v>82</v>
       </c>
       <c t="s" r="E136" s="4">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="F136" s="4">
         <v>54</v>
@@ -21899,7 +21896,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR136" s="4">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="AS136" s="4">
         <v>60</v>
@@ -21941,7 +21938,7 @@
         <v>75</v>
       </c>
       <c t="s" r="E137" s="4">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c t="s" r="F137" s="4">
         <v>54</v>
@@ -22098,7 +22095,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E138" s="4">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="F138" s="4">
         <v>54</v>
@@ -22213,7 +22210,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR138" s="4">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="AS138" s="4">
         <v>60</v>
@@ -22370,7 +22367,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR139" s="4">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="AS139" s="4">
         <v>60</v>
@@ -22527,7 +22524,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR140" s="4">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="AS140" s="4">
         <v>60</v>
@@ -22569,7 +22566,7 @@
         <v>93</v>
       </c>
       <c t="s" r="E141" s="4">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="F141" s="4">
         <v>54</v>
@@ -22684,7 +22681,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR141" s="4">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="AS141" s="4">
         <v>60</v>
@@ -22724,7 +22721,7 @@
       </c>
       <c r="D142" s="4"/>
       <c t="s" r="E142" s="4">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="F142" s="4">
         <v>54</v>
@@ -22881,7 +22878,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E143" s="4">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="F143" s="4">
         <v>54</v>
@@ -22996,7 +22993,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR143" s="4">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="AS143" s="4">
         <v>60</v>
@@ -23038,7 +23035,7 @@
         <v>143</v>
       </c>
       <c t="s" r="E144" s="4">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c t="s" r="F144" s="4">
         <v>54</v>
@@ -23193,7 +23190,7 @@
         <v>143</v>
       </c>
       <c t="s" r="E145" s="4">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c t="s" r="F145" s="4">
         <v>54</v>
@@ -23221,7 +23218,7 @@
         <v>574</v>
       </c>
       <c r="O145" s="6">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="P145" s="7">
         <v>5.2454547202797199</v>
@@ -23239,16 +23236,16 @@
         <v>0.70860927152317876</v>
       </c>
       <c r="U145" s="9">
-        <v>0.022321428571428572</v>
+        <v>0.026490066225165563</v>
       </c>
       <c r="V145" s="9">
-        <v>0.0089285714285714281</v>
+        <v>0.0099337748344370865</v>
       </c>
       <c r="W145" s="9">
         <v>0</v>
       </c>
       <c r="X145" s="9">
-        <v>0.0089285714285714281</v>
+        <v>0.013245033112582781</v>
       </c>
       <c r="Y145" s="9">
         <v>0</v>
@@ -23257,28 +23254,28 @@
         <v>0</v>
       </c>
       <c r="AA145" s="9">
-        <v>0</v>
+        <v>0.0033112582781456954</v>
       </c>
       <c r="AB145" s="9">
-        <v>0.0089285714285714281</v>
+        <v>0.0066225165562913907</v>
       </c>
       <c r="AC145" s="9">
         <v>0</v>
       </c>
       <c r="AD145" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE145" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF145" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG145" s="6">
         <v>0</v>
       </c>
       <c r="AH145" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI145" s="6">
         <v>0</v>
@@ -23287,7 +23284,7 @@
         <v>0</v>
       </c>
       <c r="AK145" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL145" s="6">
         <v>2</v>
@@ -23348,7 +23345,7 @@
         <v>52</v>
       </c>
       <c t="s" r="E146" s="4">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c t="s" r="F146" s="4">
         <v>54</v>
@@ -23463,7 +23460,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR146" s="4">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="AS146" s="4">
         <v>60</v>
@@ -23496,7 +23493,7 @@
         <v>19910</v>
       </c>
       <c r="B147" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C147" s="4">
         <v>51</v>
@@ -23505,7 +23502,7 @@
         <v>132</v>
       </c>
       <c t="s" r="E147" s="4">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="F147" s="4">
         <v>54</v>
@@ -23527,67 +23524,67 @@
       </c>
       <c r="L147" s="4"/>
       <c r="M147" s="5">
-        <v>28628.285000000003</v>
+        <v>32053.990000000002</v>
       </c>
       <c r="N147" s="6">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="O147" s="6">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="P147" s="7">
-        <v>4.4687250996015937</v>
+        <v>4.7780780780780781</v>
       </c>
       <c r="Q147" s="8">
-        <v>13.221140939597316</v>
+        <v>13.528803589743591</v>
       </c>
       <c r="R147" s="8">
-        <v>3.1062500000000002</v>
+        <v>2.7982090909090909</v>
       </c>
       <c r="S147" s="8">
         <v>8</v>
       </c>
       <c r="T147" s="9">
-        <v>0.79865771812080533</v>
+        <v>0.74871794871794872</v>
       </c>
       <c r="U147" s="9">
-        <v>0.52348993288590606</v>
+        <v>0.51282051282051277</v>
       </c>
       <c r="V147" s="9">
-        <v>0.033557046979865772</v>
+        <v>0.035897435897435895</v>
       </c>
       <c r="W147" s="9">
-        <v>0</v>
+        <v>0.0051282051279999998</v>
       </c>
       <c r="X147" s="9">
-        <v>0.013422818791946308</v>
+        <v>0.010256410256410256</v>
       </c>
       <c r="Y147" s="9">
-        <v>0.013422818791946308</v>
+        <v>0.010256410256410256</v>
       </c>
       <c r="Z147" s="9">
         <v>0</v>
       </c>
       <c r="AA147" s="9">
-        <v>0.48322147651006714</v>
+        <v>0.47179487179487178</v>
       </c>
       <c r="AB147" s="9">
-        <v>0.013422818791946308</v>
+        <v>0.010256410256410256</v>
       </c>
       <c r="AC147" s="9">
-        <v>0.026845637583892617</v>
+        <v>0.020512820512820513</v>
       </c>
       <c r="AD147" s="6">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="AE147" s="6">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AF147" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG147" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH147" s="6">
         <v>2</v>
@@ -23599,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="AK147" s="6">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="AL147" s="6">
         <v>2</v>
@@ -23620,7 +23617,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR147" s="4">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="AS147" s="4">
         <v>60</v>
@@ -23662,7 +23659,7 @@
         <v>93</v>
       </c>
       <c t="s" r="E148" s="4">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="F148" s="4">
         <v>54</v>
@@ -23777,7 +23774,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR148" s="4">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c t="s" r="AS148" s="4">
         <v>60</v>
@@ -23810,7 +23807,7 @@
         <v>19912</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>51</v>
@@ -23819,7 +23816,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E149" s="4">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="F149" s="4">
         <v>54</v>
@@ -23841,86 +23838,86 @@
       </c>
       <c r="L149" s="4"/>
       <c r="M149" s="5">
-        <v>32776.951666666668</v>
+        <v>34499.090000000004</v>
       </c>
       <c r="N149" s="6">
-        <v>309</v>
+        <v>387</v>
       </c>
       <c r="O149" s="6">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="P149" s="7">
-        <v>6.483276369863014</v>
+        <v>6.1212081743869211</v>
       </c>
       <c r="Q149" s="8">
-        <v>16.105017741935484</v>
+        <v>15.638466666666668</v>
       </c>
       <c r="R149" s="8">
-        <v>1.9391348066298344</v>
+        <v>1.8009380952380953</v>
       </c>
       <c r="S149" s="8">
         <v>8</v>
       </c>
       <c r="T149" s="9">
-        <v>0.46774193548387094</v>
+        <v>0.51898734177215189</v>
       </c>
       <c r="U149" s="9">
-        <v>0.19354838709677419</v>
+        <v>0.21518987341772153</v>
       </c>
       <c r="V149" s="9">
-        <v>0.048387096774193547</v>
+        <v>0.046413502109704644</v>
       </c>
       <c r="W149" s="9">
         <v>0</v>
       </c>
       <c r="X149" s="9">
-        <v>0.021505376344086023</v>
+        <v>0.021097046413502109</v>
       </c>
       <c r="Y149" s="9">
-        <v>0.0053763440860215058</v>
+        <v>0.0042194092827004216</v>
       </c>
       <c r="Z149" s="9">
         <v>0</v>
       </c>
       <c r="AA149" s="9">
-        <v>0.12903225806451613</v>
+        <v>0.13924050632911392</v>
       </c>
       <c r="AB149" s="9">
-        <v>0.016129032258064516</v>
+        <v>0.021097046413502109</v>
       </c>
       <c r="AC149" s="9">
-        <v>0.010752688172043012</v>
+        <v>0.016877637130801686</v>
       </c>
       <c r="AD149" s="6">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="AE149" s="6">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="AF149" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG149" s="6">
         <v>0</v>
       </c>
       <c r="AH149" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI149" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ149" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK149" s="6">
+        <v>33</v>
+      </c>
+      <c r="AL149" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM149" s="6">
         <v>4</v>
       </c>
-      <c r="AI149" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ149" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK149" s="6">
-        <v>24</v>
-      </c>
-      <c r="AL149" s="6">
-        <v>3</v>
-      </c>
-      <c r="AM149" s="6">
-        <v>2</v>
-      </c>
       <c r="AN149" s="9">
         <v>0</v>
       </c>
@@ -23934,7 +23931,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR149" s="4">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="AS149" s="4">
         <v>60</v>
@@ -23976,7 +23973,7 @@
         <v>110</v>
       </c>
       <c t="s" r="E150" s="4">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c t="s" r="F150" s="4">
         <v>54</v>
@@ -24091,7 +24088,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR150" s="4">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c t="s" r="AS150" s="4">
         <v>60</v>
@@ -24133,7 +24130,7 @@
         <v>143</v>
       </c>
       <c t="s" r="E151" s="4">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c t="s" r="F151" s="4">
         <v>54</v>
@@ -24190,7 +24187,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR151" s="4">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c t="s" r="AS151" s="4">
         <v>60</v>
@@ -24232,7 +24229,7 @@
         <v>77</v>
       </c>
       <c t="s" r="E152" s="4">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c t="s" r="F152" s="4">
         <v>54</v>
@@ -24347,7 +24344,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR152" s="4">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c t="s" r="AS152" s="4">
         <v>60</v>
@@ -24380,7 +24377,7 @@
         <v>19927</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>51</v>
@@ -24389,7 +24386,7 @@
         <v>77</v>
       </c>
       <c t="s" r="E153" s="4">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c t="s" r="F153" s="4">
         <v>54</v>
@@ -24411,40 +24408,40 @@
       </c>
       <c r="L153" s="4"/>
       <c r="M153" s="5">
-        <v>10598.49</v>
+        <v>11172.069999999998</v>
       </c>
       <c r="N153" s="6">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="O153" s="6">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="P153" s="7">
-        <v>8.7831924369747902</v>
+        <v>8.7278534246575337</v>
       </c>
       <c r="Q153" s="8">
-        <v>25.100215384615385</v>
+        <v>25.339675000000003</v>
       </c>
       <c r="R153" s="8">
-        <v>10.356061038961039</v>
+        <v>10.430403296703297</v>
       </c>
       <c r="S153" s="8">
         <v>7</v>
       </c>
       <c r="T153" s="9">
-        <v>0.14102564102564102</v>
+        <v>0.13043478260869565</v>
       </c>
       <c r="U153" s="9">
-        <v>0.12820512820512819</v>
+        <v>0.11956521739130435</v>
       </c>
       <c r="V153" s="9">
-        <v>0.05128205128205128</v>
+        <v>0.05434782608695652</v>
       </c>
       <c r="W153" s="9">
         <v>0</v>
       </c>
       <c r="X153" s="9">
-        <v>0.05128205128205128</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="Y153" s="9">
         <v>0</v>
@@ -24453,22 +24450,22 @@
         <v>0</v>
       </c>
       <c r="AA153" s="9">
-        <v>0.038461538461538464</v>
+        <v>0.032608695652173912</v>
       </c>
       <c r="AB153" s="9">
-        <v>0.01282051282051282</v>
+        <v>0.010869565217391304</v>
       </c>
       <c r="AC153" s="9">
         <v>0</v>
       </c>
       <c r="AD153" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE153" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF153" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG153" s="6">
         <v>0</v>
@@ -24504,7 +24501,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR153" s="4">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="AS153" s="4">
         <v>60</v>
@@ -24546,7 +24543,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E154" s="4">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c t="s" r="F154" s="4">
         <v>54</v>
@@ -24661,7 +24658,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR154" s="4">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="AS154" s="4">
         <v>60</v>
@@ -24694,7 +24691,7 @@
         <v>19930</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C155" s="4">
         <v>51</v>
@@ -24703,7 +24700,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E155" s="4">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="F155" s="4">
         <v>54</v>
@@ -24725,64 +24722,64 @@
       </c>
       <c r="L155" s="4"/>
       <c r="M155" s="5">
-        <v>32467.715</v>
+        <v>35503.389999999999</v>
       </c>
       <c r="N155" s="6">
-        <v>370</v>
+        <v>479</v>
       </c>
       <c r="O155" s="6">
-        <v>317</v>
+        <v>412</v>
       </c>
       <c r="P155" s="7">
-        <v>4.6321299465240644</v>
+        <v>5.2663573195876294</v>
       </c>
       <c r="Q155" s="8">
-        <v>23.916771293375394</v>
+        <v>23.886690533980584</v>
       </c>
       <c r="R155" s="8">
-        <v>13.831449657534247</v>
+        <v>12.972294764397905</v>
       </c>
       <c r="S155" s="8">
         <v>7</v>
       </c>
       <c r="T155" s="9">
-        <v>0.21766561514195584</v>
+        <v>0.19660194174757281</v>
       </c>
       <c r="U155" s="9">
-        <v>0.4952681388012618</v>
+        <v>0.44417475728155342</v>
       </c>
       <c r="V155" s="9">
-        <v>0.018927444794952682</v>
+        <v>0.016990291262135922</v>
       </c>
       <c r="W155" s="9">
         <v>0</v>
       </c>
       <c r="X155" s="9">
-        <v>0.034700315457413249</v>
+        <v>0.026699029126213591</v>
       </c>
       <c r="Y155" s="9">
-        <v>0.0094637223974763408</v>
+        <v>0.012135922330097087</v>
       </c>
       <c r="Z155" s="9">
         <v>0</v>
       </c>
       <c r="AA155" s="9">
-        <v>0.091482649842271294</v>
+        <v>0.084951456310679616</v>
       </c>
       <c r="AB155" s="9">
-        <v>0.022082018927444796</v>
+        <v>0.026699029126213591</v>
       </c>
       <c r="AC155" s="9">
-        <v>0.39432176656151419</v>
+        <v>0.35194174757281554</v>
       </c>
       <c r="AD155" s="6">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="AE155" s="6">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="AF155" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG155" s="6">
         <v>0</v>
@@ -24791,19 +24788,19 @@
         <v>11</v>
       </c>
       <c r="AI155" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ155" s="6">
         <v>0</v>
       </c>
       <c r="AK155" s="6">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="AL155" s="6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AM155" s="6">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="AN155" s="9">
         <v>0</v>
@@ -24818,7 +24815,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR155" s="4">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c t="s" r="AS155" s="4">
         <v>60</v>
@@ -24851,7 +24848,7 @@
         <v>19931</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24882,82 +24879,82 @@
       </c>
       <c r="L156" s="4"/>
       <c r="M156" s="5">
-        <v>26371.613333333331</v>
+        <v>30210.189999999999</v>
       </c>
       <c r="N156" s="6">
-        <v>266</v>
+        <v>352</v>
       </c>
       <c r="O156" s="6">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="P156" s="7">
-        <v>4.1655973584905661</v>
+        <v>4.2659544159544156</v>
       </c>
       <c r="Q156" s="8">
-        <v>14.92125918367347</v>
+        <v>15.776641666666668</v>
       </c>
       <c r="R156" s="8">
-        <v>3.914717021276596</v>
+        <v>4.8950672000000006</v>
       </c>
       <c r="S156" s="8">
         <v>7</v>
       </c>
       <c r="T156" s="9">
-        <v>0.54081632653061229</v>
+        <v>0.50757575757575757</v>
       </c>
       <c r="U156" s="9">
-        <v>0.17346938775510204</v>
+        <v>0.15909090909090909</v>
       </c>
       <c r="V156" s="9">
-        <v>0.061224489795918366</v>
+        <v>0.053030303030303032</v>
       </c>
       <c r="W156" s="9">
-        <v>0.010204081631999999</v>
+        <v>0.0075757575749999997</v>
       </c>
       <c r="X156" s="9">
-        <v>0.040816326530612242</v>
+        <v>0.03787878787878788</v>
       </c>
       <c r="Y156" s="9">
-        <v>0</v>
+        <v>0.007575757575757576</v>
       </c>
       <c r="Z156" s="9">
-        <v>0.01020408163265306</v>
+        <v>0.007575757575757576</v>
       </c>
       <c r="AA156" s="9">
-        <v>0.061224489795918366</v>
+        <v>0.068181818181818177</v>
       </c>
       <c r="AB156" s="9">
-        <v>0.020408163265306121</v>
+        <v>0.022727272727272728</v>
       </c>
       <c r="AC156" s="9">
         <v>0</v>
       </c>
       <c r="AD156" s="6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE156" s="6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AF156" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG156" s="6">
         <v>1</v>
       </c>
       <c r="AH156" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI156" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ156" s="6">
         <v>1</v>
       </c>
       <c r="AK156" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL156" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM156" s="6">
         <v>0</v>
@@ -24975,7 +24972,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR156" s="4">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="AS156" s="4">
         <v>60</v>
@@ -25017,7 +25014,7 @@
         <v>75</v>
       </c>
       <c t="s" r="E157" s="4">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c t="s" r="F157" s="4">
         <v>54</v>
@@ -25132,7 +25129,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR157" s="4">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="AS157" s="4">
         <v>60</v>
@@ -25329,7 +25326,7 @@
       </c>
       <c r="D159" s="4"/>
       <c t="s" r="E159" s="4">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="F159" s="4">
         <v>54</v>
@@ -25444,7 +25441,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR159" s="4">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c t="s" r="AS159" s="4">
         <v>60</v>
@@ -25477,7 +25474,7 @@
         <v>19943</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>51</v>
@@ -25486,7 +25483,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E160" s="4">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="F160" s="4">
         <v>54</v>
@@ -25508,40 +25505,40 @@
       </c>
       <c r="L160" s="4"/>
       <c r="M160" s="5">
-        <v>20663.650000000001</v>
+        <v>21234.48</v>
       </c>
       <c r="N160" s="6">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="O160" s="6">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="P160" s="7">
-        <v>7.687581372549019</v>
+        <v>7.4293195918367347</v>
       </c>
       <c r="Q160" s="8">
-        <v>20.075797391304349</v>
+        <v>19.782962962962962</v>
       </c>
       <c r="R160" s="8">
-        <v>7.6155954128440371</v>
+        <v>7.6266921874999998</v>
       </c>
       <c r="S160" s="8">
         <v>7</v>
       </c>
       <c r="T160" s="9">
-        <v>0.32173913043478258</v>
+        <v>0.31111111111111112</v>
       </c>
       <c r="U160" s="9">
-        <v>0.25862068965517243</v>
+        <v>0.26470588235294118</v>
       </c>
       <c r="V160" s="9">
-        <v>0.094827586206896547</v>
+        <v>0.095588235294117641</v>
       </c>
       <c r="W160" s="9">
         <v>0</v>
       </c>
       <c r="X160" s="9">
-        <v>0.077586206896551727</v>
+        <v>0.088235294117647065</v>
       </c>
       <c r="Y160" s="9">
         <v>0</v>
@@ -25550,28 +25547,28 @@
         <v>0</v>
       </c>
       <c r="AA160" s="9">
-        <v>0.051724137931034482</v>
+        <v>0.051470588235294115</v>
       </c>
       <c r="AB160" s="9">
-        <v>0.025862068965517241</v>
+        <v>0.029411764705882353</v>
       </c>
       <c r="AC160" s="9">
-        <v>0.068965517241379309</v>
+        <v>0.073529411764705885</v>
       </c>
       <c r="AD160" s="6">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AE160" s="6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AF160" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG160" s="6">
         <v>0</v>
       </c>
       <c r="AH160" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI160" s="6">
         <v>0</v>
@@ -25580,13 +25577,13 @@
         <v>0</v>
       </c>
       <c r="AK160" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL160" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM160" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN160" s="9">
         <v>0</v>
@@ -25601,7 +25598,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR160" s="4">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c t="s" r="AS160" s="4">
         <v>60</v>
@@ -25629,7 +25626,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="161" ht="24.75" customHeight="1">
+    <row r="161" ht="13.5" customHeight="1">
       <c r="A161" s="2">
         <v>19944</v>
       </c>
@@ -25643,7 +25640,7 @@
         <v>101</v>
       </c>
       <c t="s" r="E161" s="4">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="F161" s="4">
         <v>54</v>
@@ -25758,7 +25755,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR161" s="4">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c t="s" r="AS161" s="4">
         <v>60</v>
@@ -25797,10 +25794,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D162" s="4">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c t="s" r="E162" s="4">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c t="s" r="F162" s="4">
         <v>54</v>
@@ -25915,7 +25912,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR162" s="4">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="AS162" s="4">
         <v>60</v>
@@ -25957,7 +25954,7 @@
         <v>75</v>
       </c>
       <c t="s" r="E163" s="4">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="F163" s="4">
         <v>54</v>
@@ -26072,7 +26069,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR163" s="4">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c t="s" r="AS163" s="4">
         <v>60</v>
@@ -26114,7 +26111,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E164" s="4">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c t="s" r="F164" s="4">
         <v>54</v>
@@ -26229,7 +26226,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR164" s="4">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c t="s" r="AS164" s="4">
         <v>60</v>
@@ -26262,7 +26259,7 @@
         <v>19951</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26271,7 +26268,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E165" s="4">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c t="s" r="F165" s="4">
         <v>54</v>
@@ -26293,79 +26290,79 @@
       </c>
       <c r="L165" s="4"/>
       <c r="M165" s="5">
-        <v>30525.634999999998</v>
+        <v>32665.860000000004</v>
       </c>
       <c r="N165" s="6">
-        <v>280</v>
+        <v>354</v>
       </c>
       <c r="O165" s="6">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="P165" s="7">
-        <v>4.2864620938628155</v>
+        <v>4.8198005698005701</v>
       </c>
       <c r="Q165" s="8">
-        <v>15.958502721088434</v>
+        <v>16.466315263157895</v>
       </c>
       <c r="R165" s="8">
-        <v>4.654745138888889</v>
+        <v>4.7959239130434783</v>
       </c>
       <c r="S165" s="8">
         <v>7</v>
       </c>
       <c r="T165" s="9">
-        <v>0.58503401360544216</v>
+        <v>0.56315789473684208</v>
       </c>
       <c r="U165" s="9">
-        <v>0.1360544217687075</v>
+        <v>0.1368421052631579</v>
       </c>
       <c r="V165" s="9">
-        <v>0.027210884353741496</v>
+        <v>0.026315789473684209</v>
       </c>
       <c r="W165" s="9">
-        <v>0</v>
+        <v>0.005263157894</v>
       </c>
       <c r="X165" s="9">
-        <v>0.027210884353741496</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="Y165" s="9">
-        <v>0.020408163265306121</v>
+        <v>0.026315789473684209</v>
       </c>
       <c r="Z165" s="9">
         <v>0</v>
       </c>
       <c r="AA165" s="9">
-        <v>0.074829931972789115</v>
+        <v>0.089473684210526316</v>
       </c>
       <c r="AB165" s="9">
         <v>0</v>
       </c>
       <c r="AC165" s="9">
-        <v>0.013605442176870748</v>
+        <v>0.010526315789473684</v>
       </c>
       <c r="AD165" s="6">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AE165" s="6">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AF165" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG165" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH165" s="6">
         <v>4</v>
       </c>
       <c r="AI165" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ165" s="6">
         <v>0</v>
       </c>
       <c r="AK165" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL165" s="6">
         <v>0</v>
@@ -26374,7 +26371,7 @@
         <v>2</v>
       </c>
       <c r="AN165" s="9">
-        <v>0.027210884353741496</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="AO165" s="6">
         <v>4</v>
@@ -26386,7 +26383,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR165" s="4">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c t="s" r="AS165" s="4">
         <v>60</v>
@@ -26419,7 +26416,7 @@
         <v>19954</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>51</v>
@@ -26428,7 +26425,7 @@
         <v>90</v>
       </c>
       <c t="s" r="E166" s="4">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="F166" s="4">
         <v>54</v>
@@ -26450,40 +26447,40 @@
       </c>
       <c r="L166" s="4"/>
       <c r="M166" s="5">
-        <v>11861.021666666667</v>
+        <v>14056.930000000002</v>
       </c>
       <c r="N166" s="6">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="O166" s="6">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="P166" s="7">
-        <v>5.5646508064516134</v>
+        <v>6.4324712643678161</v>
       </c>
       <c r="Q166" s="8">
-        <v>16.369608823529411</v>
+        <v>17.236667368421053</v>
       </c>
       <c r="R166" s="8">
-        <v>3.3235294117647061</v>
+        <v>3.4554389473684211</v>
       </c>
       <c r="S166" s="8">
         <v>7</v>
       </c>
       <c r="T166" s="9">
-        <v>0.48529411764705882</v>
+        <v>0.43157894736842106</v>
       </c>
       <c r="U166" s="9">
-        <v>0.058823529411764705</v>
+        <v>0.073684210526315783</v>
       </c>
       <c r="V166" s="9">
         <v>0</v>
       </c>
       <c r="W166" s="9">
-        <v>0.029411764704999999</v>
+        <v>0.021052631578000001</v>
       </c>
       <c r="X166" s="9">
-        <v>0.014705882352941176</v>
+        <v>0.010526315789473684</v>
       </c>
       <c r="Y166" s="9">
         <v>0</v>
@@ -26492,19 +26489,19 @@
         <v>0</v>
       </c>
       <c r="AA166" s="9">
-        <v>0</v>
+        <v>0.010526315789473684</v>
       </c>
       <c r="AB166" s="9">
-        <v>0.014705882352941176</v>
+        <v>0.031578947368421054</v>
       </c>
       <c r="AC166" s="9">
         <v>0</v>
       </c>
       <c r="AD166" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE166" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF166" s="6">
         <v>0</v>
@@ -26522,10 +26519,10 @@
         <v>0</v>
       </c>
       <c r="AK166" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL166" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM166" s="6">
         <v>0</v>
@@ -26543,7 +26540,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR166" s="4">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c t="s" r="AS166" s="4">
         <v>60</v>
@@ -26585,7 +26582,7 @@
         <v>75</v>
       </c>
       <c t="s" r="E167" s="4">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c t="s" r="F167" s="4">
         <v>54</v>
@@ -26700,7 +26697,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR167" s="4">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c t="s" r="AS167" s="4">
         <v>60</v>
@@ -26739,10 +26736,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D168" s="4">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="E168" s="4">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c t="s" r="F168" s="4">
         <v>54</v>
@@ -26857,7 +26854,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR168" s="4">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c t="s" r="AS168" s="4">
         <v>60</v>
@@ -26890,7 +26887,7 @@
         <v>19959</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>51</v>
@@ -26899,7 +26896,7 @@
         <v>110</v>
       </c>
       <c t="s" r="E169" s="4">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c t="s" r="F169" s="4">
         <v>54</v>
@@ -26921,85 +26918,85 @@
       </c>
       <c r="L169" s="4"/>
       <c r="M169" s="5">
-        <v>15599.266666666665</v>
+        <v>21463.259999999998</v>
       </c>
       <c r="N169" s="6">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="O169" s="6">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="P169" s="7">
-        <v>5.1270114942528737</v>
+        <v>5.4958180811808122</v>
       </c>
       <c r="Q169" s="8">
-        <v>15.303402040816326</v>
+        <v>15.339167499999999</v>
       </c>
       <c r="R169" s="8">
-        <v>3.7564612244897959</v>
+        <v>3.6717092105263154</v>
       </c>
       <c r="S169" s="8">
         <v>7</v>
       </c>
       <c r="T169" s="9">
-        <v>0.55102040816326525</v>
+        <v>0.48749999999999999</v>
       </c>
       <c r="U169" s="9">
-        <v>0.12244897959183673</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="V169" s="9">
-        <v>0.081632653061224483</v>
+        <v>0.0625</v>
       </c>
       <c r="W169" s="9">
         <v>0</v>
       </c>
       <c r="X169" s="9">
-        <v>0.020408163265306121</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="Y169" s="9">
-        <v>0</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="Z169" s="9">
         <v>0</v>
       </c>
       <c r="AA169" s="9">
-        <v>0.020408163265306121</v>
+        <v>0.087499999999999994</v>
       </c>
       <c r="AB169" s="9">
         <v>0</v>
       </c>
       <c r="AC169" s="9">
-        <v>0</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="AD169" s="6">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AE169" s="6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AF169" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG169" s="6">
         <v>0</v>
       </c>
       <c r="AH169" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI169" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ169" s="6">
         <v>0</v>
       </c>
       <c r="AK169" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AL169" s="6">
         <v>0</v>
       </c>
       <c r="AM169" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN169" s="9">
         <v>0</v>
@@ -27014,7 +27011,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR169" s="4">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c t="s" r="AS169" s="4">
         <v>60</v>
@@ -27047,7 +27044,7 @@
         <v>19961</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>51</v>
@@ -27056,7 +27053,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E170" s="4">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c t="s" r="F170" s="4">
         <v>54</v>
@@ -27078,70 +27075,70 @@
       </c>
       <c r="L170" s="4"/>
       <c r="M170" s="5">
-        <v>17508.866666666665</v>
+        <v>19774.209999999999</v>
       </c>
       <c r="N170" s="6">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="O170" s="6">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="P170" s="7">
-        <v>5.8112528662420386</v>
+        <v>6.5477780952380957</v>
       </c>
       <c r="Q170" s="8">
-        <v>17.066270238095239</v>
+        <v>18.166060909090909</v>
       </c>
       <c r="R170" s="8">
-        <v>5.0861842105263158</v>
+        <v>5.0305558823529415</v>
       </c>
       <c r="S170" s="8">
         <v>7</v>
       </c>
       <c r="T170" s="9">
-        <v>0.34523809523809523</v>
+        <v>0.30909090909090908</v>
       </c>
       <c r="U170" s="9">
-        <v>0.25</v>
+        <v>0.24545454545454545</v>
       </c>
       <c r="V170" s="9">
-        <v>0</v>
+        <v>0.0090909090909090905</v>
       </c>
       <c r="W170" s="9">
         <v>0</v>
       </c>
       <c r="X170" s="9">
-        <v>0.047619047619047616</v>
+        <v>0.054545454545454543</v>
       </c>
       <c r="Y170" s="9">
-        <v>0.035714285714285712</v>
+        <v>0.027272727272727271</v>
       </c>
       <c r="Z170" s="9">
         <v>0</v>
       </c>
       <c r="AA170" s="9">
-        <v>0.13095238095238096</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="AB170" s="9">
-        <v>0.023809523809523808</v>
+        <v>0.018181818181818181</v>
       </c>
       <c r="AC170" s="9">
-        <v>0.10714285714285714</v>
+        <v>0.10909090909090909</v>
       </c>
       <c r="AD170" s="6">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="AE170" s="6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AF170" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG170" s="6">
         <v>0</v>
       </c>
       <c r="AH170" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI170" s="6">
         <v>3</v>
@@ -27156,7 +27153,7 @@
         <v>2</v>
       </c>
       <c r="AM170" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AN170" s="9">
         <v>0</v>
@@ -27171,7 +27168,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR170" s="4">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c t="s" r="AS170" s="4">
         <v>60</v>
@@ -27204,7 +27201,7 @@
         <v>19962</v>
       </c>
       <c r="B171" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C171" s="4">
         <v>51</v>
@@ -27213,7 +27210,7 @@
         <v>52</v>
       </c>
       <c t="s" r="E171" s="4">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c t="s" r="F171" s="4">
         <v>54</v>
@@ -27235,31 +27232,31 @@
       </c>
       <c r="L171" s="4"/>
       <c r="M171" s="5">
-        <v>11633.276666666665</v>
+        <v>20752.619999999999</v>
       </c>
       <c r="N171" s="6">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="O171" s="6">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="P171" s="7">
-        <v>8.3061403508771932</v>
+        <v>11.62681511111111</v>
       </c>
       <c r="Q171" s="8">
-        <v>32.322617857142859</v>
+        <v>30.771199122807019</v>
       </c>
       <c r="R171" s="8">
-        <v>17.529629629629628</v>
+        <v>12.72157767857143</v>
       </c>
       <c r="S171" s="8">
         <v>7</v>
       </c>
       <c r="T171" s="9">
-        <v>0</v>
+        <v>0.043859649122807015</v>
       </c>
       <c r="U171" s="9">
-        <v>0.2857142857142857</v>
+        <v>0.14035087719298245</v>
       </c>
       <c r="V171" s="9">
         <v>0</v>
@@ -27268,28 +27265,28 @@
         <v>0</v>
       </c>
       <c r="X171" s="9">
-        <v>0</v>
+        <v>0.026315789473684209</v>
       </c>
       <c r="Y171" s="9">
-        <v>0</v>
+        <v>0.008771929824561403</v>
       </c>
       <c r="Z171" s="9">
         <v>0</v>
       </c>
       <c r="AA171" s="9">
-        <v>0.035714285714285712</v>
+        <v>0.035087719298245612</v>
       </c>
       <c r="AB171" s="9">
-        <v>0.071428571428571425</v>
+        <v>0.026315789473684209</v>
       </c>
       <c r="AC171" s="9">
-        <v>0.17857142857142858</v>
+        <v>0.061403508771929821</v>
       </c>
       <c r="AD171" s="6">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AE171" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AF171" s="6">
         <v>0</v>
@@ -27298,22 +27295,22 @@
         <v>0</v>
       </c>
       <c r="AH171" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI171" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ171" s="6">
         <v>0</v>
       </c>
       <c r="AK171" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL171" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM171" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN171" s="9">
         <v>0</v>
@@ -27328,7 +27325,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR171" s="4">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="AS171" s="4">
         <v>60</v>
@@ -27370,7 +27367,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E172" s="4">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c t="s" r="F172" s="4">
         <v>54</v>
@@ -27485,7 +27482,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR172" s="4">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c t="s" r="AS172" s="4">
         <v>60</v>
@@ -27527,7 +27524,7 @@
         <v>52</v>
       </c>
       <c t="s" r="E173" s="4">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c t="s" r="F173" s="4">
         <v>54</v>
@@ -27584,7 +27581,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR173" s="4">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c t="s" r="AS173" s="4">
         <v>60</v>
@@ -27626,7 +27623,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E174" s="4">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c t="s" r="F174" s="4">
         <v>54</v>
@@ -27783,7 +27780,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E175" s="4">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c t="s" r="F175" s="4">
         <v>54</v>
@@ -27870,10 +27867,10 @@
     </row>
     <row r="176" ht="13.5" customHeight="1">
       <c t="s" r="A176" s="11">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c t="s" r="B176" s="11">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C176" s="12"/>
       <c r="D176" s="12"/>
@@ -27886,91 +27883,91 @@
       <c r="K176" s="12"/>
       <c r="L176" s="12"/>
       <c t="s" r="M176" s="11">
+        <v>290</v>
+      </c>
+      <c t="s" r="N176" s="11">
+        <v>291</v>
+      </c>
+      <c t="s" r="O176" s="11">
         <v>292</v>
       </c>
-      <c t="s" r="N176" s="11">
+      <c t="s" r="P176" s="11">
         <v>293</v>
       </c>
-      <c t="s" r="O176" s="11">
+      <c t="s" r="Q176" s="11">
         <v>294</v>
       </c>
-      <c t="s" r="P176" s="11">
+      <c t="s" r="R176" s="11">
         <v>295</v>
       </c>
-      <c t="s" r="Q176" s="11">
+      <c t="s" r="S176" s="11">
         <v>296</v>
       </c>
-      <c t="s" r="R176" s="11">
+      <c t="s" r="T176" s="11">
         <v>297</v>
       </c>
-      <c t="s" r="S176" s="11">
+      <c t="s" r="U176" s="11">
         <v>298</v>
       </c>
-      <c t="s" r="T176" s="11">
+      <c t="s" r="V176" s="11">
         <v>299</v>
       </c>
-      <c t="s" r="U176" s="11">
+      <c t="s" r="W176" s="11">
         <v>300</v>
       </c>
-      <c t="s" r="V176" s="11">
+      <c t="s" r="X176" s="11">
         <v>301</v>
       </c>
-      <c t="s" r="W176" s="11">
+      <c t="s" r="Y176" s="11">
         <v>302</v>
       </c>
-      <c t="s" r="X176" s="11">
+      <c t="s" r="Z176" s="11">
         <v>303</v>
       </c>
-      <c t="s" r="Y176" s="11">
+      <c t="s" r="AA176" s="11">
         <v>304</v>
       </c>
-      <c t="s" r="Z176" s="11">
-        <v>302</v>
-      </c>
-      <c t="s" r="AA176" s="11">
+      <c t="s" r="AB176" s="11">
         <v>305</v>
       </c>
-      <c t="s" r="AB176" s="11">
+      <c t="s" r="AC176" s="11">
         <v>306</v>
       </c>
-      <c t="s" r="AC176" s="11">
+      <c t="s" r="AD176" s="11">
         <v>307</v>
       </c>
-      <c t="s" r="AD176" s="11">
+      <c t="s" r="AE176" s="11">
         <v>308</v>
       </c>
-      <c t="s" r="AE176" s="11">
+      <c t="s" r="AF176" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="AF176" s="11">
+      <c t="s" r="AG176" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="AG176" s="11">
+      <c t="s" r="AH176" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="AH176" s="11">
+      <c t="s" r="AI176" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="AI176" s="11">
+      <c t="s" r="AJ176" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="AJ176" s="11">
+      <c t="s" r="AK176" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="AK176" s="11">
+      <c t="s" r="AL176" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="AL176" s="11">
+      <c t="s" r="AM176" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="AM176" s="11">
+      <c t="s" r="AN176" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="AN176" s="11">
+      <c t="s" r="AO176" s="11">
         <v>318</v>
-      </c>
-      <c t="s" r="AO176" s="11">
-        <v>319</v>
       </c>
       <c r="AP176" s="12"/>
       <c t="s" r="AQ176" s="12">
@@ -27987,10 +27984,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX176" s="11">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c t="s" r="AY176" s="11">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AZ176" s="12"/>
       <c r="BA176" s="12"/>
